--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,26 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,16 +766,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="11" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -792,45 +786,47 @@
       </c>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>29.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.6</v>
+        <v>23.8</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y4" s="3" t="n">
-        <v>76.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
@@ -846,21 +842,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>8.800000000000001</v>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>14.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -872,38 +874,44 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>262</v>
+        <v>14.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="O5" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>92.7</v>
+        <v>2</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S5" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>7.2</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>70.2</v>
+        <v>14.4</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
+        <v>18.6</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X5" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y5" s="3" t="n">
         <v>6.8</v>
       </c>
@@ -921,70 +929,69 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>15.2</v>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>14.4</v>
+        <v>1.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>20.8</v>
+        <v>1.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Q6" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>26.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="U6" s="3" t="n"/>
+        <v>81.2</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>61.5</v>
+      </c>
       <c r="V6" s="3" t="n">
-        <v>23.9</v>
+        <v>5.1</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>74.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>4.2</v>
@@ -1003,70 +1010,76 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="9" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>10.6</v>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
+        <v>0.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>20.3</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>17.5</v>
+        <v>2.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O7" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>19.5</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>26.8</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>21.2</v>
+        <v>41.3</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>86.2</v>
+        <v>4.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="inlineStr">
@@ -1083,67 +1096,71 @@
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="9" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>8.4</v>
+      <c r="D8" s="11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>10.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.4</v>
+        <v>15.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>18.9</v>
+        <v>4.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>25.8</v>
+        <v>20.1</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S8" s="8" t="n">
-        <v>66.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>5.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>21.4</v>
+        <v>19.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>59.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1160,69 +1177,67 @@
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="9" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="3" t="n">
-        <v>57.8</v>
+      <c r="D9" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>8.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>57.8</v>
+        <v>1.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>2.1</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.2</v>
+        <v>18.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>11.4</v>
+        <v>2.1</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>94.2</v>
+      </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n">
-        <v>318.6</v>
+        <v>2.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.8</v>
+        <v>4.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.6</v>
+        <v>1.4</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>110.8</v>
+        <v>2.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>23.6</v>
+        <v>2.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>382.2</v>
+        <v>5.2</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1239,67 +1254,69 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>23.7</v>
+      <c r="D10" s="12" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>23.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>19.6</v>
+        <v>5.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>16.2</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>591.2</v>
-      </c>
-      <c r="O10" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>52.1</v>
+      </c>
       <c r="P10" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>19.1</v>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n">
-        <v>24.5</v>
+        <v>6.3</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>23.8</v>
+        <v>48.8</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>26.9</v>
+        <v>19.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>16.2</v>
+        <v>38.6</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>31.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
@@ -1316,67 +1333,69 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>23.7</v>
+      <c r="D11" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>43.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>81</v>
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M11" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>92.59999999999999</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>2.1</v>
+        <v>94.2</v>
       </c>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.4</v>
+        <v>2</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>26.7</v>
+        <v>2</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>24.8</v>
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.2</v>
+        <v>2.2</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>22.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1393,67 +1412,75 @@
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>18.5</v>
+      <c r="D12" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+577
+</t>
+        </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N12" s="3" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>29.6</v>
+      </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>0.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>934.8</v>
+        <v>8.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
+        <v>25.1</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="T12" s="3" t="n">
-        <v>0.1</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>24.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22.9</v>
+        <v>4.8</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>26.8</v>
+        <v>25.4</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>81.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="inlineStr">
@@ -1470,67 +1497,71 @@
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E13" s="9" t="n">
+      <c r="D13" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="M13" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="O13" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="P13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>24.3</v>
+        <v>93.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>62.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="U13" s="3" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V13" s="3" t="n">
-        <v>21.8</v>
+        <v>2.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>24.4</v>
+        <v>46.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1547,71 +1578,69 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="9" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>16.5</v>
+      <c r="D14" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>18.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>6.8</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.2</v>
+        <v>2</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.4</v>
+        <v>25.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>2.9</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>25.2</v>
-      </c>
+        <v>6.3</v>
+      </c>
+      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
-        <v>83.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="inlineStr">
@@ -1628,67 +1657,71 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>22.5</v>
+      <c r="D15" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>22.6</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>16.5</v>
+        <v>98.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.9</v>
+        <v>1.5</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
+        <v>18.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>46.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" s="3" t="n"/>
+        <v>3.8</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V15" s="3" t="n">
-        <v>22.8</v>
+        <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>26.4</v>
+        <v>12.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>17.2</v>
+        <v>85.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>51.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="inlineStr">
@@ -1705,69 +1738,67 @@
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="10" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>116.6</v>
+      <c r="D16" s="12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>2.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>13.9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>92.3</v>
+        <v>1.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>2.7</v>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>951.3</v>
+        <v>19.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>953.2</v>
-      </c>
+        <v>24.7</v>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>5.3</v>
+        <v>92.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>26.6</v>
+        <v>12.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>22.9</v>
+        <v>42.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>18.2</v>
+        <v>5.2</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1841.7</v>
+        <v>2.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>20.9</v>
+        <v>2.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>24.4</v>
+        <v>26.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1784,65 +1815,71 @@
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="D17" s="12" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>4.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="3" t="n"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>42.9</v>
+      </c>
       <c r="R17" s="8" t="n">
-        <v>26.6</v>
+        <v>46.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>26.6</v>
+        <v>5.7</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>22.9</v>
+        <v>16.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>704.3</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>2.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>85.3</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>151</v>
+        <v>0.2</v>
       </c>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
@@ -1859,67 +1896,71 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
-        <v>25.1</v>
+      <c r="D18" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9.6</v>
+        <v>48.1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="I18" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n">
-        <v>21.5</v>
+        <v>4.1</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>24.8</v>
+        <v>14.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>82.2</v>
+        <v>48.3</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
@@ -1936,69 +1977,71 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="12" t="n">
-        <v>3</v>
+      <c r="D19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>13.8</v>
+        <v>8.5</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J19" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>6262.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n">
-        <v>981.2</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.8</v>
-      </c>
       <c r="W19" s="3" t="n">
-        <v>254.3</v>
+        <v>4.8</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>85.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2015,69 +2058,71 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>12.9</v>
+      <c r="D20" s="11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>17.6</v>
+        <v>46.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>28.3</v>
+        <v>2.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="3" t="n"/>
+        <v>85.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>19.9</v>
+        <v>32.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>19.8</v>
+        <v>2</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.2</v>
+        <v>4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>20.2</v>
+        <v>2.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>1.9</v>
+        <v>258.3</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2094,69 +2139,71 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="9" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>9.6</v>
+      <c r="D21" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>12.6</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>19.2</v>
+        <v>18.3</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>28</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>292.2</v>
+        <v>393.2</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92.2</v>
+        <v>927.2</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>12.8</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.9</v>
+        <v>18.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22</v>
+        <v>25.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="U21" s="3" t="n"/>
+        <v>20.2</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>29.2</v>
+      </c>
       <c r="V21" s="3" t="n">
-        <v>19.9</v>
+        <v>2.2</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>90.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2173,71 +2220,71 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>23.2</v>
+      <c r="D22" s="11" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>23.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.2</v>
+        <v>3.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="K22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="Q22" s="3" t="n">
-        <v>28.5</v>
+        <v>2.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>29.9</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>26.2</v>
+        <v>42.8</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>80.2</v>
+        <v>15.3</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2254,71 +2301,71 @@
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="10" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>119.2</v>
+      <c r="D23" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>2.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.9</v>
+        <v>1.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>68.8</v>
+        <v>15.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>389.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>96.2</v>
+        <v>3.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>185.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>18.6</v>
+        <v>2.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.8</v>
+        <v>1393.2</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.4</v>
+        <v>26</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.9</v>
+        <v>41.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>119.9</v>
+        <v>1.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>536</v>
+        <v>25.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>37.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>12.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>22.9</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>427.8</v>
+        <v>230.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2335,66 +2382,68 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E24" s="10" t="n">
+      <c r="D24" s="12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>282.8</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n">
-        <v>98.8</v>
-      </c>
       <c r="M24" s="3" t="n">
-        <v>19.2</v>
+        <v>1.7</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>391.2</v>
+        <v>20</v>
       </c>
       <c r="P24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>23.5</v>
-      </c>
       <c r="X24" s="3" t="n">
-        <v>85.2</v>
+        <v>80.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
@@ -2414,71 +2463,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>24.9</v>
+      <c r="D25" s="10" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.1</v>
+        <v>5.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>2.2</v>
       </c>
       <c r="I25" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>0.8</v>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 1
+</t>
+        </is>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2495,69 +2547,71 @@
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>23.9</v>
+      <c r="D26" s="10" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2.8</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I26" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="K26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24</v>
-      </c>
       <c r="X26" s="3" t="n">
-        <v>80.2</v>
+        <v>8.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2574,69 +2628,71 @@
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
-      <c r="D27" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>9.9</v>
+      <c r="D27" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>12.9</v>
       </c>
       <c r="I27" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="L27" s="3" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.2</v>
+        <v>19.1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>10</v>
+        <v>93.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>39.3</v>
+        <v>25.8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>5.6</v>
+        <v>0.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>34.9</v>
+        <v>6.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22</v>
+        <v>2.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>28.2</v>
+        <v>24.5</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>53.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2653,71 +2709,71 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="9" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>24.3</v>
+      <c r="D28" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>19.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>958.4</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>92.2</v>
+        <v>29.1</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.6</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>21.2</v>
+        <v>2.1</v>
       </c>
       <c r="S28" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>853.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="Y28" s="3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>2.3</v>
       </c>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2734,71 +2790,71 @@
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
-      <c r="D29" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>19.7</v>
+      <c r="D29" s="11" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>16.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>35.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.2</v>
+        <v>16.8</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>651.1</v>
+        <v>682.5</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>90.2</v>
+        <v>92.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>451.6</v>
+        <v>2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>26.4</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W29" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>82.59999999999999</v>
+        <v>2.2</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2815,71 +2871,71 @@
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
-      <c r="D30" s="10" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>1.3</v>
+      <c r="D30" s="12" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>4.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>1.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>11.3</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>92.8</v>
+        <v>18.5</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>4.5</v>
+        <v>3908.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>91.2</v>
+        <v>2.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.1</v>
+        <v>26.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>26.9</v>
+        <v>12.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>922.2</v>
+        <v>322.2</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>44.2</v>
+        <v>49.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>82.8</v>
+        <v>134.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>20.8</v>
+        <v>1042.6</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>22.9</v>
+        <v>14.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>17.2</v>
+        <v>322.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6.5</v>
+        <v>24.4</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2896,69 +2952,71 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="9" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>19.8</v>
+      <c r="D31" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>58.2</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L31" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>18.5</v>
+      <c r="M31" s="8" t="n">
+        <v>751.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>4</v>
+        <v>452.6</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>39.7</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2644.4</v>
+        <v>28.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>15.5</v>
+        <v>48.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>3</v>
+        <v>63.5</v>
       </c>
       <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2975,67 +3033,71 @@
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
-      <c r="D32" s="12" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>14.5</v>
+      <c r="D32" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>72.5</v>
+        <v>0.9</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>28.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>26.8</v>
+        <v>2.6</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>35.3</v>
+        <v>3.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>20.4</v>
+        <v>23.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>23</v>
+        <v>2.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>27.4</v>
+        <v>0.9</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>80.3</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3052,69 +3114,71 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E33" s="9" t="n">
+      <c r="D33" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.9</v>
-      </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>19.8</v>
+        <v>5.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>81.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="O33" s="3" t="n"/>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>22.9</v>
+        <v>2.3</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>4.8</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.5</v>
+        <v>24.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>86.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3130,43 +3194,51 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>12.7</v>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="8" t="n">
-        <v>81.2</v>
+        <v>0.9</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>78.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>928.2</v>
+        <v>1.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3175,25 +3247,25 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>24.6</v>
+        <v>29.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>24.2</v>
+        <v>2.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>62.8</v>
+        <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3210,69 +3282,67 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>89.40000000000001</v>
+      <c r="D35" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>25.8</v>
       </c>
       <c r="G35" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>18.2</v>
-      </c>
       <c r="I35" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M35" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="N35" s="8" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>928.2</v>
-      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n">
-        <v>27.9</v>
+        <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>33.6</v>
+        <v>53.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.8</v>
+        <v>45.1</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.9</v>
+        <v>4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>22.8</v>
+        <v>6.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3288,68 +3358,76 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>23.6</v>
+        <v>30.4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>25.8</v>
+        <v>18.4</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>2.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>454.2</v>
+        <v>18.2</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>2.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="n">
-        <v>8090.2</v>
-      </c>
-      <c r="O36" s="3" t="n"/>
+      <c r="N36" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U36" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>67.59999999999999</v>
+      <c r="V36" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>58.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>37.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3366,69 +3444,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="10" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>392.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>126.9</v>
+      <c r="D37" s="12" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>25.8</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>84634.39999999999</v>
+        <v>4.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>1.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>1.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1441.8</v>
+        <v>0.3</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="O37" s="3" t="n"/>
+        <v>9450.299999999999</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>7.5</v>
+        <v>12.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>26.9</v>
+        <v>48.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>10.3</v>
+        <v>90.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.9</v>
+        <v>1242.1</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>22.2</v>
+        <v>1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>25.2</v>
+        <v>125.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>13.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>4.3</v>
+        <v>32.4</v>
       </c>
       <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3445,38 +3525,36 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="10" t="n">
-        <v>421.2</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>25.4</v>
+      <c r="D38" s="12" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>26.3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>13.9</v>
+        <v>9.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17.4</v>
+        <v>81</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>1.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>8338.4</v>
-      </c>
+        <v>85.7</v>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n">
-        <v>81.8</v>
+        <v>9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.2</v>
@@ -3485,31 +3563,31 @@
         <v>2.6</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>11.6</v>
+        <v>25.8</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>23.5</v>
+        <v>2.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>17.9</v>
+        <v>14.1</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>24.8</v>
+        <v>48.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>21.6</v>
+        <v>2.4</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3526,67 +3604,69 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n">
-        <v>32.8</v>
+      <c r="D39" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>51.6</v>
+        <v>18.9</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>54.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>14.1</v>
+        <v>0.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.4</v>
+        <v>12.4</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>21.3</v>
+        <v>32.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.1</v>
+        <v>4.1</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="N39" s="3" t="n">
-        <v>19.8</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>28.6</v>
+        <v>18.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.2</v>
+        <v>6.2</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>72.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>194.4</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3602,70 +3682,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="9" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>14.2</v>
+      <c r="C40" s="3" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>14.1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>98.3</v>
+        <v>17</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>27.8</v>
+        <v>18.2</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>27.8</v>
+        <v>4.3</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.6</v>
+        <v>2.9</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.9</v>
+        <v>2.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>12.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z40" s="3" t="n"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -3681,65 +3763,71 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="9" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F41" s="9" t="n">
+      <c r="C41" s="3" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F41" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>12.8</v>
+      <c r="G41" s="11" t="n">
+        <v>14.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>18.5</v>
+        <v>2.9</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="N41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O41" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>31.2</v>
+        <v>3.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>25.1</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3758,69 +3846,69 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>25.6</v>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>25.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>72.8</v>
+        <v>12.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>21</v>
+        <v>2.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3.6</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>1.8</v>
+        <v>89</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>922.1</v>
+      <c r="N42" s="3" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>14.8</v>
+        <v>4.1</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="T42" s="3" t="n"/>
+      <c r="T42" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
+        <v>24.8</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>2.6</v>
@@ -3839,26 +3927,24 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>12.5</v>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1.1</v>
+        <v>12.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3.6</v>
@@ -3866,37 +3952,57 @@
       <c r="K43" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+      <c r="L43" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+6
+</t>
+        </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>381.9</v>
+        <v>6.8</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>95.3</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>95.7</v>
+        <v>85.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>27.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.2</v>
+        <v>24.3</v>
       </c>
       <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -3913,63 +4019,78 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="9" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>-25.3</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <v>54.7</v>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4262
+7
+</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2429
+14
+</t>
+        </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+7
+</t>
+        </is>
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>366.3</v>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77 777
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="8" t="n">
-        <v>6.9</v>
+      <c r="P44" s="3" t="n">
+        <v>106.5</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="S44" s="8" t="n">
-        <v>121.3</v>
+        <v>41.8</v>
       </c>
       <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.8</v>
+        <v>2.4</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.2</v>
+      <c r="X44" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>5.4</v>
+        <v>50.4</v>
       </c>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
@@ -3986,29 +4107,29 @@
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
-      <c r="D45" s="9" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E45" s="9" t="n">
+      <c r="D45" s="12" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E45" s="12" t="n">
         <v>18.7</v>
       </c>
-      <c r="F45" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>13.7</v>
+      <c r="F45" s="12" t="n">
+        <v>192.9</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.1</v>
+        <v>45.5</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.5</v>
+        <v>282.8</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>18.4</v>
@@ -4016,19 +4137,25 @@
       <c r="M45" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n">
-        <v>98.3</v>
-      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="R45" s="3" t="n">
-        <v>25.7</v>
+        <v>5.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>60.2</v>
+        <v>6.2</v>
       </c>
       <c r="T45" s="3" t="n"/>
       <c r="U45" s="3" t="n">
@@ -4036,11 +4163,8 @@
       </c>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
+      <c r="X45" s="3" t="n">
+        <v>83.2</v>
       </c>
       <c r="Y45" s="3" t="n"/>
       <c r="Z45" s="3" t="n"/>
@@ -4057,60 +4181,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="10" t="n">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E46" s="10" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>0.1</v>
+      <c r="E46" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>25.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="8" t="n">
+        <v>290.1</v>
+      </c>
       <c r="V46" s="8" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>150.1</v>
-      </c>
+      <c r="W46" s="3" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,16 +152,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -765,15 +789,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="11" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>14.8</v>
@@ -784,51 +808,49 @@
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n">
-        <v>8.9</v>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="14" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="N4" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="P4" s="3" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>851.8</v>
-      </c>
       <c r="S4" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T4" s="3" t="n"/>
+        <v>29.3</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>545.2</v>
+      </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W4" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+        <v>21.5</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -842,27 +864,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="11" t="n">
-        <v>31.7</v>
+        <v>26.2</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>16.9</v>
+        <v>11.4</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>14.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>15.3</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -874,48 +890,50 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>18.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>13.8</v>
+        <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>2</v>
+        <v>6.6</v>
+      </c>
+      <c r="Q5" s="14" t="n">
+        <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>7.2</v>
+        <v>21</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>14.4</v>
+        <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>18.6</v>
+        <v>6.5</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>26.2</v>
+        <v>23.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X5" s="14" t="n">
+        <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -929,74 +947,72 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>8.800000000000001</v>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>11.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2</v>
+        <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S6" s="8" t="n">
-        <v>7.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>61.5</v>
+        <v>207.4</v>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W6" s="14" t="n">
+        <v>51.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>86.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+        <v>77.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1010,78 +1026,70 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>15.2</v>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>31.6</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R7" s="3" t="n"/>
+        <v>20.1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>26.8</v>
+        <v>22.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>14.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>41.3</v>
+        <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>4.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="X7" s="14" t="n">
+        <v>22.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" s="3" t="n"/>
+        <v>86.2</v>
+      </c>
+      <c r="Z7" s="3" t="inlineStr"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1095,74 +1103,72 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="11" t="n">
-        <v>30.5</v>
+        <v>26.8</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>19.9</v>
+        <v>18.4</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>25.2</v>
+        <v>22.6</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>10.6</v>
+        <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>15.8</v>
+        <v>14.4</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4.4</v>
+        <v>18.9</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>22.5</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>3.5</v>
+        <v>25.8</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>5.2</v>
+        <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.2</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>19.8</v>
+        <v>8.4</v>
+      </c>
+      <c r="V8" s="14" t="n">
+        <v>94.59999999999999</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>86.2</v>
+        <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+        <v>7.3</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1176,70 +1182,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="11" t="n">
-        <v>26.8</v>
+        <v>147.4</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>18.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>22.6</v>
+        <v>118.5</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>8.4</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.3</v>
+        <v>957.8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2.1</v>
+        <v>16.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>18.9</v>
+        <v>949.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>20.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O9" s="3" t="n"/>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="n">
+        <v>1454.6</v>
+      </c>
       <c r="P9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R9" s="3" t="n"/>
+        <v>129.4</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>1110.9</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>2.2</v>
+        <v>142.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>4.2</v>
+        <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.4</v>
+        <v>1948.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>2.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>126.9</v>
+      </c>
+      <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+        <v>231.1</v>
+      </c>
+      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1253,72 +1259,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="12" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>5.8</v>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="11" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>97.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>52.1</v>
+        <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="R10" s="3" t="n"/>
+        <v>25.9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="S10" s="3" t="n">
-        <v>6.3</v>
+        <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>48.8</v>
+        <v>164.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
+      </c>
+      <c r="W10" s="14" t="n">
+        <v>282.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>38.6</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>216.2</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1332,72 +1336,70 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1.5</v>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="R11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>18.8</v>
+        <v>23.8</v>
+      </c>
+      <c r="S11" s="14" t="n">
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>23.8</v>
+        <v>161.2</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>6.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X11" s="14" t="n">
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+        <v>181.2</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1411,78 +1413,70 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>23.8</v>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>11.6</v>
+        <v>8.9</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="n">
-        <v>8.5</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>29.6</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="n">
-        <v>0.1</v>
+        <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>8.4</v>
+        <v>24.9</v>
       </c>
       <c r="R12" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>28.5</v>
-      </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>161.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>24.8</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>4.8</v>
+        <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+        <v>194.5</v>
+      </c>
+      <c r="Z12" s="3" t="inlineStr"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1496,74 +1490,68 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>2.4</v>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="14" t="n">
+        <v>19.9</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>2.3</v>
+        <v>10.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>93.8</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>62.7</v>
+        <v>46.4</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>43</v>
+        <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>81.2</v>
+        <v>20</v>
+      </c>
+      <c r="X13" s="14" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>185.2</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1577,72 +1565,72 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="11" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="14" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R14" s="14" t="n">
+        <v>923.4</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V14" s="14" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="Y14" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>51.4</v>
+      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1656,74 +1644,70 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="11" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>98.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>2.7</v>
+        <v>16.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>91</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>12.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>46.6</v>
+        <v>26.6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.8</v>
+        <v>25.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>15.2</v>
+        <v>38.2</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>2</v>
+        <v>21.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>12.4</v>
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.8</v>
+        <v>85.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
+        <v>10.3</v>
+      </c>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1737,70 +1721,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>2.5</v>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="11" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.5</v>
+        <v>0.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>13.9</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K16" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
-        <v>19.9</v>
+        <v>2.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>92.2</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>32.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>42.9</v>
+        <v>1182.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>5.2</v>
+        <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>118.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>2.2</v>
+        <v>1949.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>26.8</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>4.2</v>
+        <v>1708.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+        <v>1151</v>
+      </c>
+      <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1814,74 +1800,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="12" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>16.6</v>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="15" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="N17" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Y17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1895,74 +1873,70 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="10" t="n">
-        <v>1.8</v>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>2.3</v>
+        <v>13.8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.1</v>
+        <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.2</v>
+        <v>46.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>91.2</v>
-      </c>
+        <v>19.2</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>12.3</v>
-      </c>
+        <v>228.8</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="n">
-        <v>25.3</v>
+        <v>2.4</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>12.4</v>
+        <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>492.1</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
+      </c>
+      <c r="V18" s="14" t="n">
+        <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>48.3</v>
+        <v>85.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z18" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1976,74 +1950,66 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>9.6</v>
+      <c r="G19" s="11" t="n">
+        <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.6</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>6262.2</v>
+        <v>1.5</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>34.3</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="n">
-        <v>26.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>2</v>
+        <v>19.9</v>
+      </c>
+      <c r="R19" s="14" t="n">
+        <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>6.5</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>2.5</v>
+        <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>28.2</v>
+        <v>19.9</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>21.8</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2057,74 +2023,68 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="11" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>22.4</v>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.2</v>
+        <v>19.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46.8</v>
+        <v>48.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="14" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32.4</v>
+        <v>26.2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2</v>
+        <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>5.2</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>2.8</v>
+      <c r="V20" s="14" t="n">
+        <v>82.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>258.3</v>
+        <v>22.1</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>83.2</v>
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>9.6</v>
+      </c>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2138,74 +2098,70 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>2.9</v>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>1.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.6</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>393.2</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>927.2</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="n">
-        <v>26.2</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
+      </c>
+      <c r="R21" s="14" t="n">
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>25.2</v>
+        <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>20.2</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.2</v>
+        <v>10.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>2.2</v>
+        <v>19.1</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+        <v>10.8</v>
+      </c>
+      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2219,74 +2175,72 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="11" t="n">
-        <v>38.5</v>
+        <v>29.2</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>8.5</v>
+        <v>17.8</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.9</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>2.2</v>
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="14" t="n">
+        <v>39.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>18.4</v>
+        <v>956.2</v>
+      </c>
+      <c r="U22" s="14" t="n">
+        <v>39.9</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>42.8</v>
+        <v>22.6</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>2.9</v>
+        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>15.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>194.7</v>
+      </c>
+      <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2300,74 +2254,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="12" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="15" t="n">
+        <v>1144.1</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>22.8</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>389.4</v>
+        <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.8</v>
+        <v>2464.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>185.1</v>
+        <v>7.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>1393.2</v>
-      </c>
+        <v>1420.9</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>26</v>
+        <v>931.6</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>41.2</v>
+        <v>1121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.3</v>
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>25.2</v>
+        <v>4.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9360.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.3</v>
+        <v>1108.4</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>12.2</v>
+        <v>102.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>22.9</v>
+        <v>197.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>230.2</v>
+        <v>927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2381,74 +2329,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="12" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>3.9</v>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>829.8</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>282.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>98.8</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>8.5</v>
+        <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>360.5</v>
+        <v>27.6</v>
+      </c>
+      <c r="S24" s="14" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>13.2</v>
+        <v>728.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.4</v>
+        <v>6.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>4.6</v>
+        <v>20.5</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.2</v>
+        <v>22.5</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>80.2</v>
+        <v>85.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2462,77 +2402,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="10" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="E25" s="3" t="n">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>183.2</v>
-      </c>
       <c r="K25" s="3" t="n">
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>97.8</v>
-      </c>
+        <v>15.2</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>22.1</v>
+        <v>1192.2</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>2.8</v>
+        <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>34.2</v>
+        <v>11.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>16.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 1
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>23.2</v>
+      </c>
+      <c r="X25" s="14" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2546,74 +2481,70 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="10" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>2.8</v>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="11" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>18.8</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>53.2</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>26.2</v>
+        <v>91.5</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>4.6</v>
+        <v>27.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>2.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>6.8</v>
+        <v>716.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>24.2</v>
+        <v>5.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>8.5</v>
+        <v>24.5</v>
+      </c>
+      <c r="X26" s="14" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z26" s="3" t="inlineStr"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2627,74 +2558,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>1.1</v>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="11" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>93.8</v>
+        <v>49.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.3</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.1</v>
+        <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="14" t="n">
+        <v>21.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>6.2</v>
+        <v>24</v>
+      </c>
+      <c r="X27" s="14" t="n">
+        <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
+        <v>5.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2708,74 +2635,72 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>15.8</v>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="11" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>19.2</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>46.3</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="n">
-        <v>0.2</v>
+        <v>119080.9</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>2.6</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2.1</v>
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>25.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>853.9</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2.9</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>2.2</v>
+        <v>21</v>
+      </c>
+      <c r="W28" s="14" t="n">
+        <v>62.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z28" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2789,74 +2714,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="11" t="n">
-        <v>32.7</v>
+        <v>30.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>15.9</v>
+        <v>18.5</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>16.8</v>
+        <v>11.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>91.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>682.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>92.8</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>2</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.7</v>
+        <v>22.4</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>6.4</v>
+      <c r="S29" s="14" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>12.4</v>
+        <v>20.8</v>
+      </c>
+      <c r="V29" s="14" t="n">
+        <v>39.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="14" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z29" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2870,74 +2793,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="12" t="n">
-        <v>306.1</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>4.3</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="15" t="n">
+        <v>19498.4</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>118.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.2</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>111.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.5</v>
+        <v>31.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.5</v>
+        <v>292.7</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>3908.6</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>2.4</v>
+        <v>41.2</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.7</v>
+        <v>120.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>322.2</v>
-      </c>
+        <v>1112.3</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>49.2</v>
+        <v>153822.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>134.6</v>
+        <v>16.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1042.6</v>
+        <v>1104.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>14.6</v>
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>322.5</v>
+        <v>312.6</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>928.4</v>
+      </c>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2951,74 +2870,68 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>58.2</v>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="11" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>751.1</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>19.4</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>452.6</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>39.7</v>
+        <v>91.2</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R31" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="R31" s="14" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="T31" s="3" t="n">
-        <v>48.2</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>2.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="W31" s="14" t="n">
+        <v>22.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.3</v>
+        <v>17.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3032,74 +2945,70 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.8</v>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I32" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
+        <v>1219.6</v>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>82.90000000000001</v>
+      <c r="Q32" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>2.6</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>0.9</v>
+        <v>25.3</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>84.5</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3113,42 +3022,38 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>48.41</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>1.5</v>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>5.6</v>
+        <v>94.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>1.2</v>
+        <v>90.2</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3157,30 +3062,30 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>2.3</v>
+        <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.2</v>
+        <v>15</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>28.2</v>
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>27.4</v>
+      </c>
+      <c r="X33" s="14" t="n">
+        <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>168.8</v>
+      </c>
+      <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3194,51 +3099,39 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>3.6</v>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="11" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>5.3</v>
+        <v>19.4</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>41.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.2</v>
+        <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
+        <v>93.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.9</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>19.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="14" t="n">
+        <v>282.5</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3247,27 +3140,27 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>29.6</v>
+        <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>63.2</v>
+        <v>98</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X34" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X34" s="14" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+        <v>16.9</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3281,70 +3174,70 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>25.8</v>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.7</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N35" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R35" s="3" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
+      </c>
+      <c r="U35" s="14" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V35" s="14" t="n">
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>6.8</v>
+        <v>24.2</v>
+      </c>
+      <c r="X35" s="14" t="n">
+        <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3358,78 +3251,70 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>2.9</v>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="11" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>21.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>18.2</v>
+        <v>15.6</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>51.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.9</v>
+        <v>91.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>31.2</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q36" s="14" t="n">
+        <v>231.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S36" s="8" t="n">
-        <v>97.3</v>
+        <v>23</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U36" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.9</v>
+        <v>23.9</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>58.2</v>
+        <v>27</v>
+      </c>
+      <c r="X36" s="14" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>11.5</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3443,74 +3328,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="12" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>25.8</v>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="15" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4.5</v>
+        <v>8711</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.3</v>
+        <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.5</v>
+        <v>42.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.7</v>
+        <v>981.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>9450.299999999999</v>
-      </c>
+        <v>941</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>90.2</v>
+        <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>12.2</v>
-      </c>
       <c r="R37" s="3" t="n">
-        <v>2.4</v>
+        <v>111</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>48.8</v>
+        <v>241.3</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>90.3</v>
+        <v>100.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1242.1</v>
+        <v>124.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>125.2</v>
+        <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>267.2</v>
+        <v>367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>37.2</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3524,72 +3407,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="12" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>26.3</v>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="11" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>51.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>9.4</v>
+        <v>19.9</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>81</v>
+        <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.1</v>
+        <v>21.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>94.09999999999999</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>90.2</v>
+        <v>41</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.6</v>
+        <v>91.2</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>25.8</v>
+        <v>28.6</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>2.6</v>
+        <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>85.2</v>
+        <v>14.2</v>
+      </c>
+      <c r="U38" s="14" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="V38" s="14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.8</v>
+        <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Z38" s="3" t="n"/>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3603,72 +3484,72 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="10" t="n">
-        <v>2.3</v>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="14" t="n">
+        <v>32.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="G39" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>245.16</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
+        <v>61.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O39" s="3" t="n"/>
+      <c r="M39" s="14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>18.6</v>
+        <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6.2</v>
+        <v>1948.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>20.2</v>
+        <v>82</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+        <v>114.4</v>
+      </c>
+      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3682,74 +3563,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G40" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="3" t="n">
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L40" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="O40" s="3" t="n"/>
+        <v>42.1</v>
+      </c>
+      <c r="M40" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="n">
+        <v>92.3</v>
+      </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>18.2</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="14" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="R40" s="14" t="n">
+        <v>22.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>47.8</v>
+        <v>39.8</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>2.9</v>
+        <v>28.6</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>2.9</v>
+        <v>25.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>7.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z40" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3763,76 +3642,72 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>42.2</v>
-      </c>
+      <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="11" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>14.2</v>
+        <v>25.6</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5</v>
+        <v>28.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18.9</v>
+        <v>15.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>0.1</v>
+        <v>92.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>2.8</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="14" t="n">
+        <v>82</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>4</v>
+        <v>24.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>2.6</v>
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3846,74 +3721,70 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="11" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>25.9</v>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="16" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>10.2</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>7</v>
+        <v>54.4</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>62.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.3</v>
+        <v>9.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>19.3</v>
+        <v>28.8</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="14" t="n">
+        <v>11.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>0.1</v>
+        <v>266.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>4.1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
       <c r="R42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24.6</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="S42" s="14" t="n">
+        <v>49.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>72</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>82.2</v>
+        <v>96.3</v>
+      </c>
+      <c r="V42" s="14" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="W42" s="14" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="X42" s="14" t="n">
+        <v>271.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>216.7</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3927,84 +3798,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="11" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4018,81 +3835,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4106,68 +3872,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="12" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="E45" s="12" t="n">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E45" s="11" t="n">
         <v>18.7</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>192.9</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>3.7</v>
+      <c r="F45" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>13.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>69.8</v>
+        <v>117.5</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>282.8</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>190.9</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P45" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>5.7</v>
+        <v>22.9</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T45" s="3" t="n"/>
+        <v>160.5</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+        <v>22.8</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>24.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4181,67 +3947,38 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="8" t="n">
-        <v>290.1</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr"/>
+      <c r="F46" s="13" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="14" t="n">
+        <v>211</v>
+      </c>
+      <c r="X46" s="14" t="n">
+        <v>9885.5</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>116560.8</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,20 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,31 +146,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,54 +772,56 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="11" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E4" s="11" t="n">
+      <c r="D4" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G4" s="11" t="n">
+      <c r="F4" s="9" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="14" t="n">
-        <v>82.90000000000001</v>
+      <c r="J4" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12.4</v>
+        <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>32.6</v>
+        <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>29.3</v>
+        <v>2.9</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>545.2</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
@@ -865,23 +849,23 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>18.8</v>
+      <c r="D5" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>21.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2.8</v>
@@ -890,46 +874,46 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M5" s="14" t="n">
         <v>17.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.4</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>29.8</v>
+        <v>20.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X5" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>76.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -948,40 +932,44 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E6" s="14" t="n">
+      <c r="D6" s="12" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="12" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="J6" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M6" s="14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O6" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -993,16 +981,16 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>207.4</v>
-      </c>
-      <c r="U6" s="14" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W6" s="14" t="n">
-        <v>51.3</v>
+        <v>2.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
@@ -1011,7 +999,7 @@
         <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1027,20 +1015,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>17.8</v>
+      <c r="H7" s="8" t="n">
+        <v>79.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1051,16 +1039,18 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="14" t="n">
+      <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20.1</v>
@@ -1069,27 +1059,27 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>24.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>81.2</v>
+      </c>
+      <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="14" t="n">
-        <v>22.8</v>
+      <c r="X7" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="n">
+        <v>114.8</v>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1104,29 +1094,29 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>18.9</v>
@@ -1136,15 +1126,15 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1156,8 +1146,8 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="14" t="n">
-        <v>94.59999999999999</v>
+      <c r="V8" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1166,9 +1156,11 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1183,29 +1175,29 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>147.4</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="E9" s="10" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>118.5</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>57.8</v>
+      <c r="G9" s="3" t="n">
+        <v>51.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>957.8</v>
+        <v>5.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>949.2</v>
+        <v>47.1</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1213,9 +1205,11 @@
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>100.1</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>1454.6</v>
+        <v>451.6</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1224,26 +1218,28 @@
         <v>129.4</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1110.9</v>
+        <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>142.5</v>
+        <v>126</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>123.8</v>
+        <v>129.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>231.1</v>
+        <v>31.4</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1260,38 +1256,42 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="D10" s="12" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>97.2</v>
+      <c r="J10" s="8" t="n">
+        <v>860.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>25.9</v>
@@ -1303,25 +1303,25 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>164.2</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="14" t="n">
-        <v>282.2</v>
+      <c r="W10" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>216.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.8</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1337,67 +1337,71 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="E11" s="12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
+        <v>13.6</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K11" s="3" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="L11" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L11" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="M11" s="8" t="n">
+        <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>21.6</v>
+      </c>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S11" s="14" t="n">
-        <v>26.7</v>
+        <v>28.4</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>65.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
+        <v>14.8</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X11" s="14" t="n">
-        <v>26.8</v>
+        <v>22.7</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>181.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1413,56 +1417,62 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="11" t="n">
+      <c r="C12" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>26.5</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.9</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>81.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="8" t="n">
+        <v>22.6</v>
+      </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>161.2</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1474,9 +1484,11 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="Z12" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>164.5</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1491,44 +1503,50 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>22.7</v>
+      <c r="E13" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="14" t="n">
-        <v>19.9</v>
+        <v>12.6</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>15.8</v>
+        <v>25.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>46.4</v>
+        <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
@@ -1537,7 +1555,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1545,13 +1563,15 @@
       <c r="W13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X13" s="14" t="n">
+      <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>185.2</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>85.2</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1565,20 +1585,22 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="11" t="n">
+      <c r="C14" s="3" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="H14" s="14" t="n">
+      <c r="E14" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1588,38 +1610,40 @@
         <v>20.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M14" s="14" t="n">
-        <v>341.4</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="R14" s="14" t="n">
-        <v>923.4</v>
+      <c r="R14" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.8</v>
+        <v>2.5</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58.2</v>
+        <v>5.8</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="14" t="n">
-        <v>25.2</v>
+      <c r="V14" s="8" t="n">
+        <v>15.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>22.8</v>
@@ -1628,9 +1652,11 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>951.4</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1645,69 +1671,75 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>23.8</v>
+      <c r="D15" s="9" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>16.8</v>
+        <v>2.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>4.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>38.2</v>
+        <v>58.2</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>9.5</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Z15" s="3" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1722,69 +1754,69 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>140.8</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>92.3</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4</v>
+        <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>18.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="L16" s="3" t="n">
-        <v>2.1</v>
+        <v>951.3</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>9455.200000000001</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.5</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.2</v>
+        <v>16.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.3</v>
+        <v>1182.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>118.8</v>
+        <v>21314.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1949.2</v>
+        <v>99.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>10.1</v>
+        <v>1158.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1124.6</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>1708.8</v>
-      </c>
+        <v>11274.6</v>
+      </c>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>1151</v>
+        <v>100.5</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1800,48 +1832,54 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="15" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="C17" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G17" s="12" t="n">
         <v>9.6</v>
       </c>
-      <c r="H17" s="14" t="n">
-        <v>12.9</v>
+      <c r="H17" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>191.2</v>
+        <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>25.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>25.3</v>
+        <v>23.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>64.90000000000001</v>
@@ -1850,11 +1888,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>82.2</v>
+        <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>2</v>
@@ -1874,11 +1914,11 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>30.2</v>
+      <c r="D18" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>24.9</v>
@@ -1887,51 +1927,53 @@
         <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>46.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M18" s="14" t="n">
-        <v>11</v>
+        <v>19.8</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>228.8</v>
-      </c>
-      <c r="P18" s="14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Q18" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="R18" s="3" t="n">
-        <v>2.4</v>
+        <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.8</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>85.2</v>
+        <v>24.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>1</v>
@@ -1951,51 +1993,57 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="12" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+        <v>27.9</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>418.3</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P19" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="14" t="n">
+      <c r="R19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>23</v>
+        <v>2.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.2</v>
+        <v>18.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -2003,11 +2051,11 @@
       <c r="W19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="X19" s="14" t="n">
-        <v>21.8</v>
+      <c r="X19" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2023,42 +2071,48 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="3" t="n">
+      <c r="C20" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E20" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>19.6</v>
+      <c r="G20" s="12" t="n">
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>48.6</v>
+        <v>17.6</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>26.2</v>
+        <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
@@ -2067,22 +2121,22 @@
         <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>12.2</v>
+        <v>82.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="14" t="n">
-        <v>82.8</v>
+        <v>10.9</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>41.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2099,20 +2153,20 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>1.3</v>
+      <c r="D21" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.3</v>
+        <v>1.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2121,45 +2175,45 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>13.4</v>
-      </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="14" t="n">
-        <v>19.1</v>
+      <c r="R21" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>19.1</v>
+        <v>13.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>90.2</v>
-      </c>
+      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2176,69 +2230,71 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>23.5</v>
+      <c r="D22" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="14" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>91.2</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="14" t="n">
-        <v>39.9</v>
+      <c r="R22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>956.2</v>
-      </c>
-      <c r="U22" s="14" t="n">
-        <v>39.9</v>
+        <v>856.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>194.7</v>
+        <v>94.7</v>
       </c>
       <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2254,63 +2310,69 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="15" t="n">
-        <v>1144.1</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>290.4</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>1944.6</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>910.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>57.2</v>
+      </c>
       <c r="H23" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>220.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>72.5</v>
+      </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2464.4</v>
+        <v>21.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.9</v>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>931.6</v>
+        <v>931.2</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1121</v>
+        <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>4.8</v>
+        <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>9360.6</v>
+        <v>96</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1108.4</v>
+        <v>47.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.7</v>
+        <v>197.4</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>927.8</v>
+        <v>118.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>12.4</v>
@@ -2330,61 +2392,63 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="15" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
+      <c r="D24" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>58.9</v>
+      </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>98.8</v>
       </c>
-      <c r="M24" s="14" t="n">
-        <v>316.4</v>
+      <c r="M24" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="n">
+        <v>531.2</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S24" s="14" t="n">
-        <v>23.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>728.2</v>
+        <v>12.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="8" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>85.2</v>
-      </c>
+      <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
@@ -2403,69 +2467,69 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G25" s="11" t="n">
+      <c r="E25" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>1192.2</v>
-      </c>
-      <c r="P25" s="14" t="n">
-        <v>9</v>
+        <v>15.5</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>11.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>25.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X25" s="14" t="n">
-        <v>69.2</v>
+        <v>29.9</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>67.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>59.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2482,13 +2546,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="11" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F26" s="11" t="n">
+      <c r="D26" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2503,31 +2567,35 @@
       <c r="J26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K26" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>71.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>91.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>27.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>47.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>716.2</v>
+        <v>26.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2538,7 +2606,7 @@
       <c r="W26" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X26" s="14" t="n">
+      <c r="X26" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
@@ -2558,21 +2626,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
+      <c r="C27" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>27.3</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="12" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G27" s="12" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2581,17 +2651,19 @@
         <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>49.4</v>
+        <v>4.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
@@ -2600,26 +2672,26 @@
         <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="U27" s="3" t="inlineStr"/>
-      <c r="V27" s="14" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X27" s="14" t="n">
+      <c r="V27" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2636,69 +2708,71 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="11" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="D28" s="12" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="14" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H28" s="14" t="n">
+      <c r="G28" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="O28" s="3" t="n">
-        <v>119080.9</v>
+        <v>122.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>25.6</v>
+        <v>2.3</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W28" s="14" t="n">
-        <v>62.2</v>
+        <v>21.8</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>61.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2715,42 +2789,44 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="11" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F29" s="11" t="n">
+      <c r="D29" s="12" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>24.2</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>11.2</v>
+      <c r="G29" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>91.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="14" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="M29" s="14" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>40.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2758,26 +2834,26 @@
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="14" t="n">
+      <c r="S29" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V29" s="14" t="n">
-        <v>39.4</v>
+        <v>2.5</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X29" s="14" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2793,14 +2869,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="15" t="n">
-        <v>19498.4</v>
-      </c>
-      <c r="E30" s="15" t="n">
+      <c r="C30" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>1948.4</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F30" s="15" t="n">
+      <c r="F30" s="10" t="n">
         <v>118.1</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2810,51 +2888,53 @@
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>31.3</v>
+        <v>4.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>292.7</v>
+        <v>12.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>16.4</v>
+        <v>18.6</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>41.2</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>120.7</v>
+        <v>920.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1112.3</v>
-      </c>
-      <c r="S30" s="3" t="inlineStr"/>
+        <v>112.9</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>126.4</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>153822.2</v>
+        <v>3322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.1</v>
+        <v>1088.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1104.2</v>
+        <v>1184.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>114.6</v>
+        <v>115.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.6</v>
+        <v>108.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>928.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2871,65 +2951,69 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="11" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>19.8</v>
+      <c r="D31" s="12" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="M31" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>25.9</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="R31" s="14" t="n">
-        <v>82.59999999999999</v>
+        <v>26.3</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W31" s="14" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.3</v>
+        <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2946,26 +3030,26 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="11" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>1.3</v>
+      <c r="D32" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
@@ -2976,9 +3060,11 @@
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1219.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -2987,25 +3073,25 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>22.4</v>
+        <v>288.1</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -3022,38 +3108,44 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="11" t="n">
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>14.6</v>
+      <c r="E33" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>94.5</v>
+        <v>4.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>90.2</v>
+        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3068,22 +3160,22 @@
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
       <c r="V33" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="X33" s="14" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>168.8</v>
+        <v>165.8</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3099,42 +3191,50 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="11" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="C34" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>93.5</v>
+        <v>13.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
-      <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="14" t="n">
-        <v>282.5</v>
+      <c r="M34" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3143,22 +3243,22 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98</v>
+        <v>68.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="X34" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="X34" s="3" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>16.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3175,20 +3275,20 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="11" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>27.4</v>
+      <c r="D35" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.2</v>
+        <v>10.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3202,10 +3302,14 @@
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>30.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>994.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3220,22 +3324,22 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="U35" s="14" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V35" s="14" t="n">
-        <v>32</v>
+        <v>12.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X35" s="14" t="n">
+      <c r="X35" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.2</v>
+        <v>113.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3252,26 +3356,26 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="D36" s="12" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="H36" s="14" t="n">
-        <v>51.4</v>
+      <c r="H36" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>0.5</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3280,18 +3384,20 @@
         <v>18.9</v>
       </c>
       <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>470.6</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q36" s="14" t="n">
-        <v>231.2</v>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
@@ -3300,7 +3406,7 @@
         <v>12.6</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.3</v>
+        <v>2.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3308,11 +3414,11 @@
       <c r="W36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="X36" s="14" t="n">
-        <v>85.2</v>
+      <c r="X36" s="3" t="n">
+        <v>55.7</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3329,20 +3435,20 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="10" t="n">
         <v>1161.5</v>
       </c>
-      <c r="E37" s="15" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="F37" s="15" t="n">
+      <c r="E37" s="10" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F37" s="10" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8711</v>
+        <v>818</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
@@ -3351,47 +3457,49 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>42.2</v>
+        <v>49.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>981.1</v>
+        <v>28.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>941</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="O37" s="3" t="n">
         <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
+        <v>120.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
         <v>111</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>241.3</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>367.2</v>
+        <v>3672.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>37.2</v>
+        <v>537.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3408,40 +3516,42 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="11" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="E38" s="15" t="n">
+      <c r="D38" s="10" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="15" t="n">
-        <v>51.5</v>
+      <c r="F38" s="9" t="n">
+        <v>524.6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>41</v>
+        <v>50.7</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>91.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>28.6</v>
@@ -3450,16 +3560,16 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U38" s="14" t="n">
-        <v>274.9</v>
-      </c>
-      <c r="V38" s="14" t="n">
-        <v>22.2</v>
+        <v>14.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3468,7 +3578,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3485,39 +3595,39 @@
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="14" t="n">
-        <v>32.6</v>
+      <c r="D39" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>245.16</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>11</v>
+        <v>10.2</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="14" t="n">
-        <v>19.8</v>
+        <v>68.2</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>11.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3525,17 +3635,17 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>22.6</v>
+      <c r="R39" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>1948.2</v>
+        <v>61.6</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>28.6</v>
+        <v>21.8</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>82</v>
@@ -3544,11 +3654,9 @@
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>114.4</v>
-      </c>
+        <v>21.6</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3564,66 +3672,68 @@
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="D40" s="12" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>18.8</v>
+      <c r="G40" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="J40" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J40" s="3" t="n">
         <v>91</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M40" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="14" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="R40" s="14" t="n">
+      <c r="Q40" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>22.8</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>25.9</v>
+      <c r="W40" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3643,54 +3753,54 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="11" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="3" t="n">
+      <c r="D41" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G41" s="12" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21</v>
+        <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>28.6</v>
+        <v>4.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>15.4</v>
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>4.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>92.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="R41" s="14" t="n">
-        <v>82</v>
+        <v>2.4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.6</v>
+        <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>91</v>
+        <v>11.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
@@ -3699,10 +3809,10 @@
         <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3722,68 +3832,62 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="16" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>10.2</v>
+      <c r="D42" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>62.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>15.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="14" t="n">
-        <v>11.9</v>
+        <v>1.5</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>950.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>29.2</v>
+        <v>11.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>266.2</v>
+        <v>92.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="R42" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="S42" s="14" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="V42" s="14" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="W42" s="14" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="X42" s="14" t="n">
-        <v>271.2</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>216.7</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3798,10 +3902,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr"/>
+      <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3835,10 +3941,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3873,65 +3981,69 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="11" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G45" s="11" t="n">
-        <v>13.7</v>
+      <c r="D45" s="10" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>182</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>117.5</v>
+        <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>19.9</v>
+        <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.3</v>
+        <v>89</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>92.2</v>
+        <v>266.6</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>22.9</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>160.5</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>9.9</v>
+        <v>509.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>22.8</v>
+        <v>96.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.8</v>
+        <v>818.7</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>24.2</v>
+        <v>966.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>271.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>51.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3947,36 +4059,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D46" s="13" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="13" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="12" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="14" t="n">
-        <v>211</v>
-      </c>
-      <c r="X46" s="14" t="n">
-        <v>9885.5</v>
+      <c r="T46" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>116560.8</v>
+        <v>1211101.1</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,26 +41,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,16 +149,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,20 +778,20 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="9" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="9" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="F4" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G4" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -803,10 +809,10 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.9</v>
+        <v>8.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -818,7 +824,7 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.9</v>
+        <v>25.2</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>45.2</v>
@@ -827,7 +833,7 @@
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.5</v>
+        <v>27.5</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
@@ -848,42 +854,44 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>21.3</v>
+      <c r="F5" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>14.6</v>
+      <c r="M5" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -895,19 +903,19 @@
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.1</v>
+        <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>21.8</v>
+        <v>43.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
@@ -932,17 +940,17 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="12" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="12" t="n">
+      <c r="D6" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.5</v>
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
@@ -951,25 +959,25 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>15.4</v>
+        <v>17.4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>97.5</v>
+        <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -981,22 +989,22 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>41.3</v>
+        <v>21.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>77.2</v>
+        <v>17.8</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1015,16 +1023,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="H7" s="8" t="n">
@@ -1050,35 +1058,37 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>24.2</v>
+        <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U7" s="3" t="inlineStr"/>
+        <v>87.2</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>114.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1093,27 +1103,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="12" t="n">
+      <c r="C8" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="11" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.4</v>
@@ -1141,13 +1153,13 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>66.2</v>
+        <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>24.6</v>
+        <v>2.4</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1156,10 +1168,10 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>59.2</v>
+        <v>69.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1175,17 +1187,17 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <v>147.4</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="F9" s="10" t="n">
+      <c r="E9" s="11" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>5.7</v>
@@ -1194,13 +1206,13 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.6</v>
+        <v>16.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>47.1</v>
+        <v>944.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1209,7 +1221,7 @@
         <v>100.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.6</v>
+        <v>452.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1221,16 +1233,16 @@
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>129.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>11</v>
@@ -1239,7 +1251,7 @@
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1255,29 +1267,33 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="12" t="n">
+      <c r="C10" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>19.6</v>
+      <c r="G10" s="8" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>860.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
@@ -1285,7 +1301,7 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
@@ -1306,7 +1322,7 @@
         <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
@@ -1321,7 +1337,7 @@
         <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1337,68 +1353,66 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>21.6</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>65.7</v>
+      <c r="R11" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
+        <v>6.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
@@ -1418,22 +1432,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D12" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.1</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>81.5</v>
+        <v>17.3</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
@@ -1442,7 +1456,7 @@
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
@@ -1450,7 +1464,7 @@
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1460,34 +1474,34 @@
         <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.8</v>
+        <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>164.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1509,20 +1523,20 @@
       <c r="E13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>2.2</v>
+      <c r="F13" s="3" t="n">
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>27.5</v>
+        <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
@@ -1534,7 +1548,7 @@
         <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1543,7 +1557,7 @@
         <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>20.4</v>
@@ -1555,7 +1569,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1585,22 +1599,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>133.1</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>14.2</v>
+      <c r="E14" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>24.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1616,28 +1628,26 @@
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
+        <v>19.7</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.4</v>
+        <v>31.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>5.8</v>
+        <v>88.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1652,10 +1662,10 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>17.2</v>
+        <v>717.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>951.4</v>
+        <v>51.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1670,45 +1680,47 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="9" t="n">
-        <v>39.19</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="C15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G15" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>12.1</v>
+        <v>29.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>2.6</v>
@@ -1716,8 +1728,8 @@
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>4.8</v>
+      <c r="S15" s="8" t="n">
+        <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1728,8 +1740,8 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>9.5</v>
+      <c r="W15" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
@@ -1738,7 +1750,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1754,29 +1766,29 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
-        <v>140.8</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>116.6</v>
+      <c r="D16" s="13" t="n">
+        <v>1940.4</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>114.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>951.3</v>
@@ -1788,35 +1800,35 @@
         <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9455.200000000001</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>16.2</v>
+        <v>122.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.9</v>
+        <v>1127.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>21314.2</v>
+        <v>18.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1158.5</v>
+        <v>984.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>11274.6</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>100.5</v>
+        <v>10064.6</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1832,19 +1844,17 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="13" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E17" s="13" t="n">
         <v>19.3</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G17" s="12" t="n">
+      <c r="F17" s="13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1854,41 +1864,39 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="M17" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>35.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>222.3</v>
+        <v>22.7</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>21.5</v>
@@ -1914,23 +1922,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="8" t="n">
-        <v>8.9</v>
+      <c r="D18" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.8</v>
+        <v>18.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.9</v>
+        <v>1.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.6</v>
@@ -1939,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
@@ -1952,7 +1960,7 @@
         <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>2.1</v>
+        <v>29.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1961,16 +1969,16 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>54.8</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>24.3</v>
@@ -1992,21 +2000,23 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="12" t="n">
+      <c r="C19" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F19" s="12" t="n">
+      <c r="E19" s="11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="11" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.5</v>
+        <v>46.9</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.3</v>
@@ -2017,8 +2027,8 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>418.3</v>
+      <c r="L19" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>18.2</v>
@@ -2037,13 +2047,13 @@
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>2.4</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -2071,19 +2081,17 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F20" s="12" t="n">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2102,9 +2110,11 @@
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O20" s="3" t="n">
         <v>90.2</v>
       </c>
@@ -2118,22 +2128,22 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>82.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41.8</v>
+        <v>81.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2153,8 +2163,8 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="n">
-        <v>28.7</v>
+      <c r="D21" s="14" t="n">
+        <v>1.5</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2163,10 +2173,10 @@
         <v>21.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2175,7 +2185,7 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>19.4</v>
@@ -2191,19 +2201,19 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>11.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>13.5</v>
@@ -2231,25 +2241,25 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E22" s="9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E22" s="14" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>23.2</v>
+      <c r="F22" s="8" t="n">
+        <v>32.8</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.2</v>
+        <v>23.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2258,10 +2268,10 @@
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>10.8</v>
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99.2</v>
@@ -2279,7 +2289,7 @@
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>856.2</v>
+        <v>8956.200000000001</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
@@ -2310,57 +2320,55 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>1944.6</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>910.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>112.8</v>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="13" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>119.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.2</v>
+        <v>5.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>220.8</v>
+        <v>85.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>72.5</v>
+        <v>2.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>21.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>931.2</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
         <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>107.2</v>
+        <v>107.9</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>47.9</v>
@@ -2369,13 +2377,13 @@
         <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>19.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>118.8</v>
+        <v>94927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2392,58 +2400,58 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F24" s="10" t="n">
+      <c r="D24" s="11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="G24" s="11" t="n">
+        <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>58.9</v>
+        <v>8.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>98.8</v>
+        <v>88.8</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>531.2</v>
+        <v>581.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>21</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>823.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>12.2</v>
+        <v>78.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="8" t="n">
-        <v>81.7</v>
+      <c r="V24" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>20.5</v>
@@ -2466,40 +2474,40 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E25" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E25" s="14" t="n">
         <v>1.8</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>42.4</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>15.5</v>
+        <v>24.2</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2514,22 +2522,22 @@
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>29.9</v>
+        <v>23.1</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>67.8</v>
+        <v>71.3</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>59.1</v>
+        <v>9.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2546,20 +2554,20 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2568,34 +2576,32 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>2.3</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>71.8</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>47.9</v>
+        <v>27.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>26.2</v>
+        <v>76.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2626,53 +2632,51 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E27" s="12" t="n">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="11" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>91.2</v>
+        <v>18.8</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2681,9 +2685,9 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V27" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W27" s="3" t="inlineStr"/>
@@ -2691,7 +2695,7 @@
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2708,44 +2712,44 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="12" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F28" s="12" t="n">
+      <c r="D28" s="11" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F28" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>18.8</v>
+      <c r="G28" s="11" t="n">
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>21.1</v>
+        <v>0.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>122.2</v>
+        <v>1272.4</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
@@ -2753,26 +2757,26 @@
       <c r="R28" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>74</v>
+      <c r="S28" s="3" t="n">
+        <v>27.6</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>61.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>17.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2789,23 +2793,23 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>1.9</v>
+      <c r="G29" s="11" t="n">
+        <v>11.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2817,13 +2821,11 @@
         <v>19.2</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>4.8</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>8</v>
@@ -2834,7 +2836,7 @@
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2847,13 +2849,13 @@
         <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>28.8</v>
+        <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2869,17 +2871,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1948.4</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>118.1</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="13" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2894,47 +2894,47 @@
         <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>12.4</v>
+        <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.6</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>920.7</v>
+        <v>130.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>112.9</v>
+        <v>112.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>3322.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1088.1</v>
+        <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1184.1</v>
+        <v>18.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>108.4</v>
+        <v>374.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2951,14 +2951,14 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="12" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>18.8</v>
+      <c r="D31" s="11" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>11.9</v>
@@ -2973,35 +2973,35 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
-        <v>1</v>
+      <c r="L31" s="8" t="n">
+        <v>10.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>22.5</v>
+      <c r="R31" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.6</v>
@@ -3013,7 +3013,7 @@
         <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>14.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -3031,40 +3031,38 @@
       </c>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E32" s="9" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E32" s="14" t="n">
         <v>1.8</v>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>2.5</v>
+      <c r="F32" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="H32" s="8" t="n">
-        <v>11.8</v>
+      <c r="H32" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>29.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -3073,15 +3071,15 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="U32" s="8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
@@ -3091,7 +3089,7 @@
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -3108,17 +3106,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>25.8</v>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>1.4</v>
@@ -3127,7 +3123,7 @@
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.5</v>
@@ -3135,17 +3131,15 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
+      <c r="M33" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="n">
         <v>10.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3154,28 +3148,28 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.6</v>
+        <v>12.8</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>165.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3191,19 +3185,17 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E34" s="12" t="n">
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E34" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="11" t="n">
         <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3213,28 +3205,28 @@
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>51.1</v>
+      <c r="M34" s="8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3243,10 +3235,10 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>69.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3258,7 +3250,7 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3275,20 +3267,20 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="9" t="n">
-        <v>0.4</v>
+      <c r="D35" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>0.8</v>
+        <v>19.4</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>10.2</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3300,16 +3292,16 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>30.1</v>
+        <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>994.2</v>
+        <v>172.4</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3324,13 +3316,13 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>12.2</v>
+        <v>192.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
@@ -3339,7 +3331,7 @@
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>113.2</v>
+        <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3356,26 +3348,26 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="12" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F36" s="12" t="n">
+      <c r="D36" s="14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>15.6</v>
+      <c r="G36" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3383,12 +3375,12 @@
       <c r="L36" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M36" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>470.6</v>
+        <v>70.7</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3397,13 +3389,13 @@
         <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>2.8</v>
@@ -3415,10 +3407,10 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>55.7</v>
+        <v>8.5</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3435,71 +3427,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="10" t="n">
-        <v>1161.5</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="F37" s="10" t="n">
+      <c r="D37" s="11" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>126.9</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>9.4</v>
+      <c r="G37" s="11" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>818</v>
+        <v>81</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>949.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>28.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>721</v>
+        <v>92</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.6</v>
+        <v>950.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>120.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.6</v>
+        <v>1230.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>101</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.1</v>
+        <v>12.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3672.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>537.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3516,39 +3508,39 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="10" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E38" s="10" t="n">
+      <c r="D38" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="9" t="n">
-        <v>524.6</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H38" s="8" t="n">
+      <c r="F38" s="11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>14.5</v>
+        <v>9.9</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>7.2</v>
+        <v>46.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>50.7</v>
+        <v>30.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
@@ -3560,7 +3552,7 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>14.9</v>
@@ -3569,7 +3561,7 @@
         <v>24.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>82.2</v>
+        <v>22.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3578,7 +3570,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3599,35 +3591,35 @@
         <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>35.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>19</v>
+        <v>17.9</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>81</v>
+        <v>19.9</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>13</v>
+        <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>796</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3635,26 +3627,26 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.6</v>
+        <v>69.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
@@ -3672,29 +3664,29 @@
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
@@ -3702,8 +3694,8 @@
       <c r="M40" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>11.8</v>
+      <c r="N40" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3711,17 +3703,17 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S40" s="8" t="n">
-        <v>60.8</v>
+      <c r="Q40" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>192.6</v>
+        <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>22.8</v>
@@ -3729,11 +3721,11 @@
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>51.8</v>
+      <c r="W40" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>8.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3753,16 +3745,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="F41" s="12" t="n">
+      <c r="D41" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G41" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3772,24 +3764,22 @@
         <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>4.9</v>
+      <c r="L41" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>99.2</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="n">
         <v>2.4</v>
       </c>
@@ -3800,19 +3790,19 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>11.8</v>
+        <v>2.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.4</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>2.2</v>
+        <v>68.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3832,39 +3822,37 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="E42" s="14" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="L42" s="8" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -3877,12 +3865,14 @@
       <c r="R42" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="S42" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="8" t="n">
-        <v>1</v>
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="V42" s="3" t="inlineStr"/>
       <c r="W42" s="3" t="inlineStr"/>
@@ -3905,9 +3895,9 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="11" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3944,9 +3934,9 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3981,41 +3971,41 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="13" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="13" t="n">
         <v>24.6</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>182</v>
+      <c r="F45" s="13" t="n">
+        <v>162</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>18.8</v>
+        <v>5.4</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>14.1</v>
+        <v>141.1</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>89</v>
+        <v>8.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>266.6</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
@@ -4028,22 +4018,22 @@
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>509.7</v>
+        <v>32.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.2</v>
+        <v>95.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>818.7</v>
+        <v>22.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>966.3</v>
+        <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>271.2</v>
+        <v>221.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4060,17 +4050,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="11" t="n">
         <v>32.3</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="11" t="n">
         <v>18.7</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F46" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>93.7</v>
+      <c r="G46" s="11" t="n">
+        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
@@ -4078,21 +4068,23 @@
       <c r="I46" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
-        <v>18.1</v>
+      <c r="J46" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>42.7</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>19.3</v>
+        <v>11.9</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4115,10 +4107,10 @@
         <v>24.2</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1211101.1</v>
+        <v>87208.5</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,13 +164,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,10 +814,10 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -817,7 +829,7 @@
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="11" t="n">
         <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -881,10 +893,10 @@
       <c r="K5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -896,7 +908,7 @@
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -911,7 +923,7 @@
       <c r="U5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="15" t="n">
         <v>43.9</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -964,10 +976,10 @@
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -979,7 +991,7 @@
       <c r="P6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -1035,7 +1047,7 @@
       <c r="G7" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="12" t="n">
         <v>79.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1047,10 +1059,10 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="11" t="n">
         <v>20.4</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
@@ -1060,7 +1072,7 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
@@ -1130,10 +1142,10 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1143,7 +1155,7 @@
       <c r="P8" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1158,7 +1170,7 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="15" t="n">
         <v>2.4</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1208,13 +1220,13 @@
       <c r="J9" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="16" t="n">
         <v>944.1</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="16" t="n">
         <v>92.8</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="16" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1226,10 +1238,10 @@
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="16" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="16" t="n">
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1241,10 +1253,10 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="16" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="16" t="n">
         <v>11</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1279,7 +1291,7 @@
       <c r="F10" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="12" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1294,10 +1306,10 @@
       <c r="K10" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1309,10 +1321,10 @@
       <c r="P10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="16" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1324,10 +1336,10 @@
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="16" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="16" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1368,7 +1380,7 @@
       <c r="H11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="12" t="n">
         <v>11.8</v>
       </c>
       <c r="J11" s="3" t="n">
@@ -1377,10 +1389,10 @@
       <c r="K11" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="15" t="n">
         <v>0.7</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1393,7 +1405,7 @@
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="15" t="n">
         <v>2.3</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1408,7 +1420,7 @@
       <c r="V11" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="11" t="n">
         <v>22.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1491,7 +1503,7 @@
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1541,7 +1553,7 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="12" t="n">
         <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1574,7 +1586,7 @@
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="11" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1652,10 +1664,10 @@
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="V14" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1722,13 +1734,13 @@
       <c r="P15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="15" t="n">
         <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="12" t="n">
         <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
@@ -1740,7 +1752,7 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1766,13 +1778,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="16" t="n">
         <v>1940.4</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="16" t="n">
         <v>44.3</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="16" t="n">
         <v>114.6</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1787,13 +1799,13 @@
       <c r="J16" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="16" t="n">
         <v>3.2</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="16" t="n">
         <v>951.3</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="16" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1805,10 +1817,10 @@
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="16" t="n">
         <v>122.2</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="16" t="n">
         <v>1127.3</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1820,10 +1832,10 @@
       <c r="U16" s="3" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="16" t="n">
         <v>984.8</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="16" t="n">
         <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
@@ -1845,13 +1857,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="16" t="n">
         <v>29.9</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="16" t="n">
         <v>19.3</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="16" t="n">
         <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1867,10 +1879,10 @@
         <v>4.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="16" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="16" t="n">
         <v>18.3</v>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
@@ -1880,13 +1892,13 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="16" t="n">
         <v>51.8</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="16" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="12" t="n">
         <v>35.3</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1895,10 +1907,10 @@
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="16" t="n">
         <v>22.7</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1946,10 +1958,10 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
@@ -2027,7 +2039,7 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2106,7 +2118,7 @@
       <c r="K20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="11" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2121,7 +2133,7 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="15" t="n">
         <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2136,7 +2148,7 @@
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="15" t="n">
         <v>81.8</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2163,7 +2175,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="15" t="n">
         <v>1.5</v>
       </c>
       <c r="E21" s="3" t="n">
@@ -2187,7 +2199,7 @@
       <c r="K21" s="3" t="n">
         <v>73.8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2203,7 +2215,7 @@
       <c r="Q21" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="15" t="n">
         <v>1.9</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2243,10 +2255,10 @@
       <c r="D22" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="15" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="12" t="n">
         <v>32.8</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2264,7 +2276,7 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="11" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -2282,7 +2294,7 @@
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="15" t="n">
         <v>2.3</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2321,13 +2333,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="16" t="n">
         <v>194.4</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="16" t="n">
         <v>10.4</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="16" t="n">
         <v>119.2</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2342,13 +2354,13 @@
       <c r="J23" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="16" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="11" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="16" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2358,10 +2370,10 @@
         <v>43.1</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="16" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="16" t="n">
         <v>107.9</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2373,10 +2385,10 @@
       <c r="U23" s="3" t="n">
         <v>47.9</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="16" t="n">
         <v>108.6</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="16" t="n">
         <v>19.7</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2422,10 +2434,10 @@
         <v>2.8</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="16" t="n">
         <v>88.8</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="16" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
@@ -2435,13 +2447,13 @@
       <c r="P24" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="16" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="S24" s="12" t="n">
         <v>823.9</v>
       </c>
       <c r="T24" s="3" t="n">
@@ -2450,10 +2462,10 @@
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="16" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="16" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
@@ -2480,7 +2492,7 @@
       <c r="D25" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="15" t="n">
         <v>1.8</v>
       </c>
       <c r="F25" s="11" t="n">
@@ -2499,10 +2511,10 @@
       <c r="K25" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="15" t="n">
         <v>42.4</v>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
+      <c r="M25" s="13" t="inlineStr"/>
       <c r="N25" s="3" t="n">
         <v>1.4</v>
       </c>
@@ -2533,7 +2545,7 @@
       <c r="W25" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="12" t="n">
         <v>71.3</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2663,7 +2675,7 @@
       <c r="M27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="12" t="n">
         <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2672,7 +2684,7 @@
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="15" t="n">
         <v>2.6</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2690,7 +2702,7 @@
       <c r="V27" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W27" s="3" t="inlineStr"/>
+      <c r="W27" s="13" t="inlineStr"/>
       <c r="X27" s="3" t="n">
         <v>80.2</v>
       </c>
@@ -2754,7 +2766,7 @@
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="15" t="n">
         <v>2.3</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2769,7 +2781,7 @@
       <c r="V28" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="12" t="n">
         <v>22.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2820,7 +2832,7 @@
       <c r="L29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
@@ -2872,13 +2884,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="16" t="n">
         <v>149.4</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="16" t="n">
         <v>8.9</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="16" t="n">
         <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2893,13 +2905,13 @@
       <c r="J30" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="16" t="n">
         <v>3.3</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="16" t="n">
         <v>92.5</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="16" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -2909,10 +2921,10 @@
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="16" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="16" t="n">
         <v>112.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2924,10 +2936,10 @@
       <c r="U30" s="3" t="n">
         <v>118.2</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="16" t="n">
         <v>18.4</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="16" t="n">
         <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -2973,10 +2985,10 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="16" t="n">
         <v>10.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="16" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -2988,10 +3000,10 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="16" t="n">
         <v>26.3</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="16" t="n">
         <v>82.8</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3003,10 +3015,10 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="16" t="n">
         <v>25.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="16" t="n">
         <v>22.8</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3033,7 +3045,7 @@
       <c r="D32" s="3" t="n">
         <v>34.8</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="15" t="n">
         <v>1.8</v>
       </c>
       <c r="F32" s="3" t="n">
@@ -3067,10 +3079,10 @@
       <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="11" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3085,7 +3097,7 @@
       <c r="V32" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3107,13 +3119,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="15" t="n">
         <v>4.2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="15" t="n">
         <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3131,7 +3143,7 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3144,10 +3156,10 @@
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="11" t="n">
         <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3162,7 +3174,7 @@
       <c r="V33" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3213,7 +3225,7 @@
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="15" t="n">
         <v>91.90000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3225,10 +3237,10 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3243,7 +3255,7 @@
       <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3306,10 +3318,10 @@
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3324,7 +3336,7 @@
       <c r="V35" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="11" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3348,7 +3360,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="14" t="n">
+      <c r="D36" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3375,7 +3387,7 @@
       <c r="L36" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="N36" s="3" t="inlineStr"/>
@@ -3385,10 +3397,10 @@
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="11" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="11" t="n">
         <v>23</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3403,7 +3415,7 @@
       <c r="V36" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="11" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3430,7 +3442,7 @@
       <c r="D37" s="11" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="16" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
@@ -3448,13 +3460,13 @@
       <c r="J37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="16" t="n">
         <v>949.9</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="16" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="16" t="n">
         <v>92</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3466,10 +3478,10 @@
       <c r="P37" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="11" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="16" t="n">
         <v>119</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3481,10 +3493,10 @@
       <c r="U37" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="16" t="n">
         <v>115</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="16" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3530,10 +3542,10 @@
         <v>9.9</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="16" t="n">
         <v>14.8</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="16" t="n">
         <v>46.8</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3545,10 +3557,10 @@
       <c r="P38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3560,10 +3572,10 @@
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="16" t="n">
         <v>22.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3614,7 +3626,7 @@
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
@@ -3627,7 +3639,7 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="15" t="n">
         <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3703,10 +3715,10 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="8" t="n">
+      <c r="Q40" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="15" t="n">
         <v>82.2</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3748,7 +3760,7 @@
       <c r="D41" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="E41" s="14" t="n">
+      <c r="E41" s="15" t="n">
         <v>17.9</v>
       </c>
       <c r="F41" s="3" t="n">
@@ -3795,7 +3807,7 @@
       <c r="U41" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="15" t="n">
         <v>2.4</v>
       </c>
       <c r="W41" s="3" t="n">
@@ -3825,7 +3837,7 @@
       <c r="D42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="14" t="n">
+      <c r="E42" s="15" t="n">
         <v>32.8</v>
       </c>
       <c r="F42" s="3" t="n">
@@ -3846,7 +3858,7 @@
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="15" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3862,7 +3874,7 @@
       <c r="Q42" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="15" t="n">
         <v>82</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -3874,8 +3886,8 @@
       <c r="U42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
+      <c r="V42" s="13" t="inlineStr"/>
+      <c r="W42" s="13" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -3895,26 +3907,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="13" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
+      <c r="R43" s="13" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="V43" s="13" t="inlineStr"/>
+      <c r="W43" s="13" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -3934,26 +3946,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="13" t="inlineStr"/>
+      <c r="W44" s="13" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -3971,13 +3983,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="16" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="16" t="n">
         <v>24.6</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="F45" s="16" t="n">
         <v>162</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -3992,13 +4004,13 @@
       <c r="J45" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="16" t="n">
         <v>2.8</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="16" t="n">
         <v>141.1</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="16" t="n">
         <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4010,8 +4022,8 @@
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="n">
+      <c r="Q45" s="14" t="inlineStr"/>
+      <c r="R45" s="16" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4023,10 +4035,10 @@
       <c r="U45" s="3" t="n">
         <v>95.2</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="16" t="n">
         <v>22.9</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="16" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4068,16 +4080,16 @@
       <c r="I46" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" s="8" t="n">
+      <c r="J46" s="12" t="n">
         <v>4.1</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="16" t="n">
         <v>42.7</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="16" t="n">
         <v>11.9</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4090,7 +4102,7 @@
         <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="16" t="n">
         <v>22.9</v>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -4100,10 +4112,10 @@
       <c r="U46" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="16" t="n">
         <v>21.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="16" t="n">
         <v>24.2</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -158,16 +158,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,16 +787,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -805,29 +811,29 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>4.5</v>
@@ -835,10 +841,10 @@
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V4" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W4" s="11" t="n">
+      <c r="V4" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W4" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -858,17 +864,17 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>81.8</v>
+      <c r="G5" s="9" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>17.3</v>
@@ -882,25 +888,25 @@
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M5" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -910,19 +916,19 @@
         <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V5" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -941,16 +947,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="9" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="E6" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G6" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -963,49 +969,49 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="9" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.8</v>
+        <v>14.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>921.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>24.9</v>
+      <c r="R6" s="9" t="n">
+        <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>390.6</v>
+        <v>50.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1024,20 +1030,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1046,12 +1052,12 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="L7" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1063,25 +1069,25 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
+        <v>87.2</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1107,16 +1113,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="9" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1131,23 +1137,23 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>791.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1159,10 +1165,10 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1172,7 +1178,7 @@
         <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>27.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1189,15 +1195,15 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="9" t="n">
-        <v>147.9</v>
+        <v>147.4</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>83.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>118.5</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="9" t="n">
         <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1207,30 +1213,30 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K9" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K9" s="15" t="n">
         <v>44.1</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>3972.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.2</v>
+        <v>454.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="15" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="15" t="n">
         <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1245,8 +1251,8 @@
       <c r="V9" s="9" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>11</v>
+      <c r="W9" s="15" t="n">
+        <v>10.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1271,16 +1277,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1290,7 +1296,7 @@
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.1</v>
@@ -1298,19 +1304,19 @@
       <c r="L10" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="9" t="n">
         <v>25.9</v>
       </c>
       <c r="R10" s="9" t="n">
@@ -1320,7 +1326,7 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>6.4</v>
+        <v>64</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1328,17 +1334,17 @@
       <c r="V10" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>2.5</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>62.8</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1354,29 +1360,29 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F11" s="11" t="n">
+      <c r="D11" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F11" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>24.3</v>
+      <c r="M11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1385,13 +1391,13 @@
         <v>91.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>29.8</v>
+      <c r="R11" s="9" t="n">
+        <v>23.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
@@ -1405,7 +1411,7 @@
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="11" t="n">
+      <c r="W11" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1431,74 +1437,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="D12" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>98.40000000000001</v>
+      <c r="G12" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q12" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R12" s="9" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2.5</v>
+        <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.3</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="11" t="n">
-        <v>21.9</v>
+      <c r="W12" s="9" t="n">
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1514,17 +1520,17 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>89.3</v>
+      <c r="G13" s="9" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1533,55 +1539,55 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.2</v>
+        <v>84.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>31.8</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="11" t="n">
+      <c r="W13" s="9" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1597,19 +1603,19 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>19.5</v>
+      <c r="E14" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>15.5</v>
@@ -1621,7 +1627,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1630,7 +1636,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1638,17 +1644,17 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="R14" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58.2</v>
+        <v>5.8</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1656,17 +1662,17 @@
       <c r="V14" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="W14" s="11" t="n">
+      <c r="W14" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>27.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>51.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1682,23 +1688,23 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1713,7 +1719,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1721,14 +1727,14 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R15" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1737,9 +1743,9 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W15" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1749,7 +1755,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1766,47 +1772,47 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>116.6</v>
+        <v>140.4</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>116.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>29.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="15" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="15" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>853.2</v>
+        <v>53.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="9" t="n">
-        <v>127.2</v>
+      <c r="Q16" s="15" t="n">
+        <v>122.2</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>122.3</v>
+        <v>112.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1815,19 +1821,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>187.8</v>
-      </c>
-      <c r="W16" s="9" t="n">
-        <v>10.8</v>
+        <v>49.2</v>
+      </c>
+      <c r="V16" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="W16" s="15" t="n">
+        <v>10.2</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>970.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1845,18 +1851,20 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="D17" s="9" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>9.1</v>
+        <v>18.5</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1865,20 +1873,20 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="15" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="9" t="n">
-        <v>18.5</v>
+      <c r="M17" s="15" t="n">
+        <v>18.8</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>91.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1893,15 +1901,15 @@
         <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="V17" s="9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V17" s="15" t="n">
         <v>22.9</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1940,7 +1948,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1951,22 +1959,22 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="10" t="n">
-        <v>1.3</v>
+      <c r="M18" s="14" t="n">
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>291.2</v>
+        <v>91.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="14" t="n">
         <v>89.2</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -1981,7 +1989,7 @@
       <c r="U18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2012,20 +2020,20 @@
       <c r="C19" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="G19" s="11" t="n">
+      <c r="D19" s="9" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G19" s="9" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.5</v>
@@ -2036,14 +2044,14 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2061,22 +2069,22 @@
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V19" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.2</v>
-      </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>87.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2095,19 +2103,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>59.6</v>
+        <v>10.1</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2121,11 +2129,11 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <v>19.8</v>
+      <c r="L20" s="9" t="n">
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
@@ -2134,29 +2142,29 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="14" t="n">
         <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>23.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="8" t="n">
-        <v>23.2</v>
+      <c r="X20" s="3" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2180,16 +2188,16 @@
       <c r="C21" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2204,13 +2212,15 @@
       <c r="K21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2220,29 +2230,29 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="10" t="n">
-        <v>1.3</v>
+      <c r="R21" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.7</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>12.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="V21" s="9" t="n">
+        <v>19.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2263,23 +2273,23 @@
       <c r="C22" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="D22" s="9" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.2</v>
@@ -2287,38 +2297,38 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>1.8</v>
+      <c r="L22" s="9" t="n">
+        <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>991.2</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>2.2</v>
+      <c r="Q22" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>86.2</v>
+        <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V22" s="10" t="n">
-        <v>2.4</v>
+      <c r="V22" s="9" t="n">
+        <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>26.2</v>
@@ -2347,46 +2357,46 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="9" t="n">
-        <v>1942.6</v>
+        <v>142.6</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="G23" s="3" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="G23" s="9" t="n">
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="9" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>1952.9</v>
+      <c r="K23" s="15" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="M23" s="15" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>951.2</v>
+        <v>458.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="15" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="15" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2398,17 +2408,17 @@
       <c r="U23" s="3" t="n">
         <v>37.7</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="15" t="n">
         <v>108.4</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="15" t="n">
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>198.7</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9425.6</v>
+        <v>27.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2427,58 +2437,58 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>28.5</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="9" t="n">
         <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>991999.1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M24" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M24" s="15" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="15" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>21.6</v>
+      <c r="R24" s="15" t="n">
+        <v>2.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2486,7 +2496,7 @@
       <c r="V24" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="15" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2496,7 +2506,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2512,20 +2522,20 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G25" s="10" t="n">
+      <c r="D25" s="9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G25" s="14" t="n">
         <v>44.4</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.1</v>
@@ -2536,47 +2546,47 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>12.9</v>
+      <c r="L25" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>59.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="14" t="n">
         <v>2.6</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="14" t="n">
         <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>31.2</v>
+        <v>71.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="14" t="n">
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>69.3</v>
+        <v>67.2</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2593,22 +2603,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F26" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F26" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.4</v>
+        <v>28.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.6</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2619,17 +2629,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="M26" s="10" t="n">
-        <v>98.96000000000001</v>
+      <c r="M26" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2641,7 +2651,7 @@
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2649,7 +2659,7 @@
       <c r="U26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2678,47 +2688,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="D27" s="9" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>9.800000000000001</v>
+      <c r="G27" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L27" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>19.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>922.2</v>
+        <v>98.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2727,12 +2737,12 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>63.2</v>
+        <v>2.5</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2761,17 +2771,17 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="11" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="D28" s="9" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>15.8</v>
+      <c r="G28" s="9" t="n">
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2785,23 +2795,23 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M28" s="10" t="n">
-        <v>1.6</v>
+      <c r="L28" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.8</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2810,19 +2820,19 @@
         <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W28" s="10" t="n">
-        <v>2.1</v>
+      <c r="W28" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2844,14 +2854,14 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="11" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>24.2</v>
+      <c r="D29" s="9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>19.7</v>
@@ -2868,15 +2878,15 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>19.2</v>
+      <c r="L29" s="9" t="n">
+        <v>18.2</v>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -2888,16 +2898,16 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>14.5</v>
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="V29" s="11" t="n">
-        <v>13.4</v>
+      <c r="V29" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2909,7 +2919,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2926,68 +2936,68 @@
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="9" t="n">
-        <v>1498.4</v>
+        <v>148.4</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>189.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>5.8</v>
+        <v>119</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="15" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="M30" s="9" t="n">
-        <v>392.1</v>
+      <c r="L30" s="15" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="M30" s="15" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="15" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>112.9</v>
+      <c r="R30" s="15" t="n">
+        <v>12.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>322.2</v>
+        <v>222.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="V30" s="9" t="n">
-        <v>104.1</v>
-      </c>
-      <c r="W30" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V30" s="15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W30" s="15" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.2</v>
+        <v>372.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>52.4</v>
+        <v>32.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>33</v>
@@ -3006,36 +3016,36 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>23.8</v>
+      <c r="D31" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.1</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M31" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M31" s="15" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>28.4</v>
+        <v>2.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3043,10 +3053,10 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="R31" s="9" t="n">
+      <c r="Q31" s="15" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="R31" s="15" t="n">
         <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3058,14 +3068,14 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="11" t="n">
+      <c r="V31" s="15" t="n">
         <v>20.8</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>47.8</v>
+      <c r="W31" s="15" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>77.8</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>6.5</v>
@@ -3089,44 +3099,44 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>23.28</v>
-      </c>
-      <c r="E32" s="10" t="n">
+      <c r="D32" s="3" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E32" s="14" t="n">
         <v>4.5</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="14" t="n">
         <v>35</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3136,22 +3146,22 @@
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>35.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W32" s="11" t="n">
+      <c r="V32" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W32" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>85.3</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3168,19 +3178,19 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="E33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>2.5</v>
+      <c r="F33" s="9" t="n">
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.4</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3191,48 +3201,48 @@
       <c r="J33" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M33" s="10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>78.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="W33" s="11" t="n">
+      <c r="V33" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="W33" s="9" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>15</v>
@@ -3250,20 +3260,22 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="11" t="n">
+      <c r="C34" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D34" s="9" t="n">
         <v>32.2</v>
       </c>
-      <c r="E34" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F34" s="11" t="n">
+      <c r="E34" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3272,26 +3284,26 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="14" t="n">
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.1</v>
+        <v>87.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3300,22 +3312,22 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.2</v>
+        <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="11" t="n">
+      <c r="W34" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>9</v>
@@ -3334,18 +3346,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="E35" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G35" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3357,25 +3369,25 @@
       <c r="J35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="10" t="n">
-        <v>1.3</v>
+      <c r="M35" s="14" t="n">
+        <v>1.8</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>28</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3385,15 +3397,15 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>129.2</v>
+        <v>15.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="W35" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3403,7 +3415,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3419,8 +3431,8 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="8" t="n">
-        <v>33.6</v>
+      <c r="D36" s="14" t="n">
+        <v>93.59999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3440,47 +3452,47 @@
       <c r="J36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="9" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="9" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>35</v>
+      <c r="R36" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>48.2</v>
+        <v>4.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="11" t="n">
+      <c r="W36" s="9" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>85.2</v>
+        <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
@@ -3505,8 +3517,8 @@
       <c r="D37" s="9" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>1929.5</v>
+      <c r="E37" s="15" t="n">
+        <v>92.5</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>126.9</v>
@@ -3524,52 +3536,52 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>949.9</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>951.1</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>0.1</v>
+        <v>49.1</v>
+      </c>
+      <c r="L37" s="15" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="M37" s="15" t="n">
+        <v>2.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.2</v>
+        <v>50.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>28.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="9" t="n">
-        <v>117.3</v>
+      <c r="R37" s="15" t="n">
+        <v>17.5</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101.3</v>
+        <v>70.3</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="15" t="n">
         <v>111</v>
       </c>
-      <c r="W37" s="11" t="n">
+      <c r="W37" s="9" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7367.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.3</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3585,14 +3597,14 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="9" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="14" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="E38" s="15" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>2.5</v>
+      <c r="F38" s="15" t="n">
+        <v>25.5</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3606,26 +3618,28 @@
       <c r="J38" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="M38" s="9" t="n">
-        <v>17.8</v>
+      <c r="K38" s="3" t="n">
+        <v>555.5</v>
+      </c>
+      <c r="L38" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="M38" s="15" t="n">
+        <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="15" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3638,19 +3652,19 @@
         <v>24.9</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="W38" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>13.2</v>
+        <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3669,7 +3683,7 @@
       <c r="D39" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="14" t="n">
         <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3678,7 +3692,7 @@
       <c r="G39" s="3" t="n">
         <v>45.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3687,18 +3701,18 @@
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L39" s="10" t="n">
-        <v>49</v>
+      <c r="K39" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3710,7 +3724,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.1</v>
+        <v>23.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3721,14 +3735,14 @@
       <c r="V39" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W39" s="10" t="n">
-        <v>2.4</v>
+      <c r="W39" s="14" t="n">
+        <v>24.17</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3749,38 +3763,38 @@
       <c r="C40" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="K40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="10" t="n">
-        <v>1.8</v>
+      <c r="M40" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3789,7 +3803,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3801,22 +3815,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>826.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3832,16 +3846,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3851,26 +3865,26 @@
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>9.1</v>
+      <c r="L41" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3879,7 +3893,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>37.8</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3897,7 +3911,7 @@
         <v>2.6</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3924,25 +3938,25 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="K42" s="3" t="n">
+      <c r="J42" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K42" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3950,26 +3964,26 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R42" s="10" t="n">
-        <v>82</v>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.6</v>
+        <v>14.5</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V42" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V42" s="14" t="n">
         <v>2.2</v>
       </c>
-      <c r="W42" s="10" t="n">
-        <v>0.7</v>
+      <c r="W42" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -3997,7 +4011,7 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="13" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="13" t="inlineStr"/>
       <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
@@ -4036,7 +4050,7 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="13" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="13" t="inlineStr"/>
       <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
@@ -4067,15 +4081,15 @@
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="9" t="n">
-        <v>122.3</v>
+        <v>129.4</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>24.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>102</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="9" t="n">
         <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4085,50 +4099,50 @@
         <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>111.9</v>
+        <v>7.7</v>
+      </c>
+      <c r="L45" s="15" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="M45" s="15" t="n">
+        <v>11.2</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>2366.2</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="R45" s="9" t="n">
+      <c r="Q45" s="15" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="R45" s="15" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>241.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>132.7</v>
+        <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v>892.7</v>
-      </c>
-      <c r="W45" s="9" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="V45" s="15" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="W45" s="15" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>19327.2</v>
+        <v>232.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>8.199999999999999</v>
@@ -4147,14 +4161,14 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="14" t="n">
         <v>1.1</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="15" t="n">
         <v>32.3</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>1.8</v>
+      <c r="F46" s="15" t="n">
+        <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>25.5</v>
@@ -4163,56 +4177,56 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L46" s="15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M46" s="15" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q46" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="J46" s="8" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L46" s="9" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="M46" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q46" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="15" t="n">
         <v>25.7</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V46" s="9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V46" s="15" t="n">
         <v>21.4</v>
       </c>
-      <c r="W46" s="9" t="n">
-        <v>2.4</v>
+      <c r="W46" s="15" t="n">
+        <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
-        <v>992.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,25 +149,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,16 +778,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -811,40 +802,40 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.1</v>
+        <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="9" t="n">
-        <v>23.8</v>
+      <c r="R4" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>4.5</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -864,16 +855,16 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -888,14 +879,14 @@
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>2</v>
+        <v>20.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>91.59999999999999</v>
@@ -903,25 +894,25 @@
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>23.1</v>
+        <v>28.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -947,16 +938,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -969,16 +960,16 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>14.8</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>91.2</v>
@@ -986,10 +977,10 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1001,17 +992,17 @@
       <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>77.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1030,16 +1021,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1054,10 +1045,10 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1069,14 +1060,14 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>87.2</v>
@@ -1084,10 +1075,10 @@
       <c r="U7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1113,16 +1104,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1137,23 +1128,23 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1165,10 +1156,10 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1194,16 +1185,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>147.4</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>118.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1213,15 +1204,15 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K9" s="15" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K9" s="14" t="n">
         <v>44.1</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1233,10 +1224,10 @@
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="15" t="n">
+      <c r="Q9" s="14" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="15" t="n">
+      <c r="R9" s="14" t="n">
         <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1248,11 +1239,11 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="15" t="n">
-        <v>10.8</v>
+      <c r="W9" s="8" t="n">
+        <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1277,20 +1268,20 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>11.6</v>
+      <c r="G10" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
@@ -1301,40 +1292,40 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>9.1</v>
+        <v>291.3</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="14" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1360,21 +1351,21 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="D11" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1393,10 +1384,10 @@
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1411,7 +1402,7 @@
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1437,17 +1428,17 @@
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F12" s="9" t="n">
+      <c r="D12" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>8.1</v>
+      <c r="G12" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
@@ -1468,7 +1459,7 @@
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
@@ -1476,10 +1467,10 @@
       <c r="P12" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q12" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1494,7 +1485,7 @@
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1520,16 +1511,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F13" s="9" t="n">
+      <c r="E13" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1551,7 +1542,7 @@
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1559,17 +1550,17 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>84.2</v>
+        <v>74.2</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3.8</v>
@@ -1577,14 +1568,14 @@
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1605,20 +1596,20 @@
       <c r="C14" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G14" s="9" t="n">
+      <c r="E14" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
@@ -1627,7 +1618,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>22.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1636,7 +1627,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1644,17 +1635,17 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>5.8</v>
+        <v>58.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1662,14 +1653,14 @@
       <c r="V14" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>77.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>5.4</v>
@@ -1688,23 +1679,23 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1719,7 +1710,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1727,14 +1718,14 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.7</v>
+        <v>10.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1745,17 +1736,17 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1771,48 +1762,48 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>140.4</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="14" t="n">
         <v>12.3</v>
       </c>
-      <c r="F16" s="15" t="n">
-        <v>116.5</v>
+      <c r="F16" s="14" t="n">
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>87.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="14" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="15" t="n">
+      <c r="M16" s="14" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>53.2</v>
+        <v>153.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="15" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>112.5</v>
+      <c r="Q16" s="8" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="R16" s="14" t="n">
+        <v>182.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1821,19 +1812,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="V16" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="W16" s="15" t="n">
-        <v>10.2</v>
+        <v>41.2</v>
+      </c>
+      <c r="V16" s="14" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="W16" s="14" t="n">
+        <v>10.1</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>408.9</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1852,18 +1843,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1873,17 +1864,17 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M17" s="15" t="n">
-        <v>18.8</v>
+      <c r="L17" s="14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.2</v>
+        <v>22.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1891,11 +1882,11 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R17" s="9" t="n">
-        <v>22.5</v>
+      <c r="R17" s="14" t="n">
+        <v>12.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>25.3</v>
@@ -1906,14 +1897,14 @@
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="V17" s="15" t="n">
+      <c r="V17" s="14" t="n">
         <v>22.9</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>82.2</v>
@@ -1948,7 +1939,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1956,17 +1947,17 @@
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="14" t="n">
-        <v>1.1</v>
+      <c r="M18" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91.2</v>
@@ -1974,10 +1965,10 @@
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="13" t="n">
         <v>89.2</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1987,10 +1978,10 @@
         <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>21.8</v>
+        <v>10.1</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>12.18</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -2018,18 +2009,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2041,17 +2032,17 @@
       <c r="J19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2062,7 +2053,7 @@
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2074,7 +2065,7 @@
       <c r="U19" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2084,7 +2075,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>87.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2103,19 +2094,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="D20" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9</v>
+        <v>29.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2124,15 +2115,15 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -2142,29 +2133,29 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R20" s="3" t="n">
+      <c r="Q20" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.7</v>
+        <v>29.7</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V20" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>85.2</v>
+        <v>25.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2188,16 +2179,16 @@
       <c r="C21" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G21" s="9" t="n">
+      <c r="E21" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2209,13 +2200,13 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2230,26 +2221,26 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>12.1</v>
+      <c r="R21" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
+        <v>28.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>90.2</v>
@@ -2271,18 +2262,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D22" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2294,17 +2285,17 @@
       <c r="J22" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="8" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91.2</v>
@@ -2315,7 +2306,7 @@
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2325,9 +2316,9 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="V22" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2356,16 +2347,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="9" t="n">
-        <v>142.6</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="14" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="E23" s="14" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="G23" s="9" t="n">
+      <c r="F23" s="14" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2377,48 +2368,48 @@
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="15" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L23" s="15" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="M23" s="15" t="n">
+      <c r="K23" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="M23" s="14" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.1</v>
+        <v>8.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>458.2</v>
+        <v>451.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="15" t="n">
+      <c r="Q23" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="15" t="n">
+      <c r="R23" s="8" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.9</v>
+        <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>36</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="V23" s="15" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="V23" s="14" t="n">
         <v>108.4</v>
       </c>
-      <c r="W23" s="15" t="n">
+      <c r="W23" s="14" t="n">
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.7</v>
+        <v>117.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>27.6</v>
+        <v>427.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2439,34 +2430,34 @@
       <c r="C24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>991999.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M24" s="15" t="n">
+      <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2478,11 +2469,11 @@
       <c r="P24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="15" t="n">
+      <c r="Q24" s="14" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="15" t="n">
-        <v>2.4</v>
+      <c r="R24" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
@@ -2493,10 +2484,10 @@
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="14" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="15" t="n">
+      <c r="W24" s="14" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2506,7 +2497,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2522,23 +2513,23 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="F25" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G25" s="14" t="n">
+      <c r="F25" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="13" t="n">
         <v>44.4</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>34.4</v>
@@ -2546,7 +2537,7 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M25" s="3" t="n">
@@ -2556,15 +2547,15 @@
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="14" t="n">
+      <c r="Q25" s="13" t="n">
         <v>2.6</v>
       </c>
-      <c r="R25" s="14" t="n">
+      <c r="R25" s="13" t="n">
         <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2579,11 +2570,11 @@
       <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="14" t="n">
+      <c r="W25" s="13" t="n">
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>67.2</v>
@@ -2605,23 +2596,23 @@
       <c r="C26" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>28.4</v>
+        <v>18.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2629,17 +2620,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2648,7 +2639,7 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.3</v>
+        <v>29.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>27.1</v>
@@ -2688,16 +2679,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2710,16 +2701,16 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="L27" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="14" t="n">
-        <v>1.8</v>
+      <c r="M27" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>19.1</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>98.2</v>
@@ -2737,7 +2728,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2771,16 +2762,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2795,23 +2786,23 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2823,16 +2814,16 @@
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>20.2</v>
+        <v>216.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2854,13 +2845,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2878,10 +2869,10 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M29" s="13" t="inlineStr"/>
+      <c r="M29" s="12" t="inlineStr"/>
       <c r="N29" s="3" t="n">
         <v>9.6</v>
       </c>
@@ -2898,7 +2889,7 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>72.2</v>
@@ -2919,7 +2910,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2935,16 +2926,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="8" t="n">
         <v>148.4</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="G30" s="9" t="n">
+      <c r="F30" s="8" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G30" s="8" t="n">
         <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -2956,41 +2947,41 @@
       <c r="J30" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K30" s="15" t="n">
+      <c r="K30" s="14" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L30" s="15" t="n">
+      <c r="L30" s="14" t="n">
         <v>92.5</v>
       </c>
-      <c r="M30" s="15" t="n">
-        <v>9.199999999999999</v>
+      <c r="M30" s="14" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="15" t="n">
+      <c r="Q30" s="14" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="15" t="n">
-        <v>12.9</v>
+      <c r="R30" s="14" t="n">
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>222.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V30" s="15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="W30" s="15" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="V30" s="14" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="W30" s="14" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3016,14 +3007,14 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="14" t="n">
         <v>29.7</v>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>23.9</v>
+      <c r="E31" s="14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>22.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
@@ -3038,14 +3029,14 @@
         <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M31" s="15" t="n">
+      <c r="L31" s="14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="M31" s="14" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>2.8</v>
+        <v>24</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3053,10 +3044,10 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="15" t="n">
+      <c r="Q31" s="14" t="n">
         <v>26.1</v>
       </c>
-      <c r="R31" s="15" t="n">
+      <c r="R31" s="14" t="n">
         <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3068,10 +3059,10 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="15" t="n">
+      <c r="V31" s="14" t="n">
         <v>20.8</v>
       </c>
-      <c r="W31" s="15" t="n">
+      <c r="W31" s="14" t="n">
         <v>22.9</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3099,47 +3090,47 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="E32" s="14" t="n">
+      <c r="D32" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="13" t="n">
         <v>4.5</v>
       </c>
-      <c r="F32" s="14" t="n">
+      <c r="F32" s="13" t="n">
         <v>35</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="13" t="inlineStr"/>
+      <c r="L32" s="12" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3151,10 +3142,10 @@
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W32" s="9" t="n">
+      <c r="V32" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3180,13 +3171,13 @@
       <c r="C33" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3201,45 +3192,45 @@
       <c r="J33" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>9</v>
+        <v>90.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>27.8</v>
+      <c r="R33" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>78.2</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V33" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>2.8</v>
@@ -3261,18 +3252,18 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D34" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3284,17 +3275,17 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="13" t="n">
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>87.2</v>
@@ -3302,10 +3293,10 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3315,12 +3306,12 @@
         <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V34" s="9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3348,16 +3339,16 @@
       <c r="C35" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3369,17 +3360,17 @@
       <c r="J35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="14" t="n">
-        <v>1.8</v>
+      <c r="M35" s="13" t="n">
+        <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.1</v>
+        <v>28.6</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>92.2</v>
@@ -3387,25 +3378,25 @@
       <c r="P35" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="V35" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3415,7 +3406,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.2</v>
+        <v>53.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3431,17 +3422,17 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="14" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="3" t="n">
+      <c r="D36" s="8" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>1.5</v>
+      <c r="G36" s="8" t="n">
+        <v>15.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
@@ -3452,17 +3443,17 @@
       <c r="J36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M36" s="14" t="n">
-        <v>1.8</v>
+      <c r="M36" s="13" t="n">
+        <v>1.2</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
@@ -3470,25 +3461,25 @@
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.4</v>
+        <v>44.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3514,13 +3505,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="E37" s="14" t="n">
         <v>92.5</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3535,32 +3526,32 @@
       <c r="J37" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>49.1</v>
       </c>
-      <c r="L37" s="15" t="n">
+      <c r="L37" s="14" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="M37" s="15" t="n">
-        <v>2.1</v>
+      <c r="M37" s="14" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>50.2</v>
+        <v>150.4</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="15" t="n">
-        <v>17.5</v>
+      <c r="R37" s="8" t="n">
+        <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.4</v>
+        <v>190.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3568,10 +3559,10 @@
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="15" t="n">
-        <v>111</v>
-      </c>
-      <c r="W37" s="9" t="n">
+      <c r="V37" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="W37" s="8" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3581,7 +3572,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>24.7</v>
+        <v>247.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3597,16 +3588,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="14" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="E38" s="15" t="n">
+      <c r="D38" s="8" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="15" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="F38" s="8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G38" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3619,16 +3610,16 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>555.5</v>
-      </c>
-      <c r="L38" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="M38" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="M38" s="14" t="n">
         <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.5</v>
+        <v>18.6</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
@@ -3636,32 +3627,32 @@
       <c r="P38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="15" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>14.1</v>
@@ -3683,7 +3674,7 @@
       <c r="D39" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E39" s="14" t="n">
+      <c r="E39" s="13" t="n">
         <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3701,18 +3692,18 @@
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3724,7 +3715,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3735,14 +3726,14 @@
       <c r="V39" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W39" s="14" t="n">
-        <v>24.17</v>
+      <c r="W39" s="13" t="n">
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3763,16 +3754,16 @@
       <c r="C40" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -3784,17 +3775,17 @@
       <c r="J40" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.1</v>
+        <v>29.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3803,7 +3794,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.2</v>
+        <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3815,22 +3806,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3846,17 +3837,17 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>12.8</v>
+      <c r="G41" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3867,7 +3858,7 @@
       <c r="J41" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
@@ -3905,7 +3896,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3927,7 +3918,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr"/>
       <c r="E42" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3938,7 +3929,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3946,7 +3937,7 @@
       <c r="J42" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -3956,7 +3947,7 @@
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3974,16 +3965,16 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V42" s="14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
+      </c>
+      <c r="V42" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W42" s="13" t="n">
+        <v>0.2</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4004,26 +3995,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="13" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
-      <c r="R43" s="13" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="13" t="inlineStr"/>
-      <c r="W43" s="13" t="inlineStr"/>
+      <c r="V43" s="12" t="inlineStr"/>
+      <c r="W43" s="12" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4043,26 +4034,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="13" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
-      <c r="R44" s="13" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="13" t="inlineStr"/>
-      <c r="W44" s="13" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4080,16 +4071,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="9" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="D45" s="14" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F45" s="14" t="n">
         <v>102</v>
       </c>
-      <c r="G45" s="9" t="n">
+      <c r="G45" s="3" t="n">
         <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4101,14 +4092,14 @@
       <c r="J45" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="L45" s="15" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M45" s="15" t="n">
-        <v>11.2</v>
+      <c r="L45" s="14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M45" s="14" t="n">
+        <v>11.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
@@ -4117,35 +4108,35 @@
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="15" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="R45" s="15" t="n">
+      <c r="Q45" s="14" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="R45" s="14" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.8</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="V45" s="15" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="V45" s="14" t="n">
         <v>85.7</v>
       </c>
-      <c r="W45" s="15" t="n">
+      <c r="W45" s="14" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>232.7</v>
+        <v>327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4161,13 +4152,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E46" s="15" t="n">
+      <c r="D46" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="14" t="n">
         <v>32.3</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="F46" s="14" t="n">
         <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4183,27 +4174,27 @@
         <v>13.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L46" s="15" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M46" s="15" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M46" s="14" t="n">
         <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2.2</v>
+        <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="Q46" s="15" t="n">
+      <c r="Q46" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="R46" s="15" t="n">
+      <c r="R46" s="14" t="n">
         <v>25.7</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4213,20 +4204,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V46" s="15" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="V46" s="14" t="n">
         <v>21.4</v>
       </c>
-      <c r="W46" s="15" t="n">
+      <c r="W46" s="14" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>2.2</v>
+        <v>298.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -812,7 +812,7 @@
         <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -820,8 +820,8 @@
       <c r="Q4" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>29.8</v>
+      <c r="R4" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>25.3</v>
@@ -886,7 +886,7 @@
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>91.59999999999999</v>
@@ -897,14 +897,14 @@
       <c r="Q5" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>28.1</v>
+        <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>70.2</v>
+        <v>7</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>6.5</v>
@@ -960,7 +960,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>17.4</v>
@@ -969,7 +969,7 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>91.2</v>
@@ -980,7 +980,7 @@
       <c r="Q6" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1002,7 +1002,7 @@
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>37.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1055,7 +1055,7 @@
         <v>2.5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
@@ -1063,11 +1063,11 @@
       <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>87.2</v>
@@ -1085,7 +1085,7 @@
         <v>24.6</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>74.2</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>23.8</v>
@@ -1126,7 +1126,7 @@
         <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>18.9</v>
@@ -1144,7 +1144,7 @@
       <c r="Q8" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1227,8 +1227,8 @@
       <c r="Q9" s="14" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="14" t="n">
-        <v>110.1</v>
+      <c r="R9" s="8" t="n">
+        <v>110.8</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>122.3</v>
@@ -1242,14 +1242,14 @@
       <c r="V9" s="8" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="8" t="n">
-        <v>110.8</v>
+      <c r="W9" s="14" t="n">
+        <v>10.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>382.6</v>
+        <v>382</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>31.1</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.2</v>
@@ -1302,7 +1302,7 @@
         <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>291.3</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
@@ -1310,7 +1310,7 @@
       <c r="Q10" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="14" t="n">
+      <c r="R10" s="8" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1365,15 +1365,15 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>12.3</v>
+      <c r="M11" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1409,7 +1409,7 @@
         <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>4.5</v>
@@ -1455,20 +1455,20 @@
       <c r="L12" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1477,10 +1477,10 @@
         <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>6.7</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1492,7 +1492,7 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>83.2</v>
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M13" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1560,7 +1560,7 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>74.2</v>
+        <v>7.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3.8</v>
@@ -1575,7 +1575,7 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>29.9</v>
@@ -1618,12 +1618,12 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1642,7 +1642,7 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58.2</v>
@@ -1706,14 +1706,14 @@
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
@@ -1725,7 +1725,7 @@
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>10.7</v>
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1775,32 +1775,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
+        <v>14.3</v>
       </c>
       <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="14" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>153.2</v>
+        <v>35.3</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="8" t="n">
-        <v>129.2</v>
+      <c r="Q16" s="14" t="n">
+        <v>10.9</v>
       </c>
       <c r="R16" s="14" t="n">
         <v>182.5</v>
@@ -1815,16 +1815,16 @@
         <v>41.2</v>
       </c>
       <c r="V16" s="14" t="n">
-        <v>116.7</v>
+        <v>11.4</v>
       </c>
       <c r="W16" s="14" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>408.9</v>
+        <v>708.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>28.1</v>
@@ -1858,7 +1858,7 @@
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.9</v>
@@ -1870,11 +1870,11 @@
       <c r="L17" s="14" t="n">
         <v>19.1</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.1</v>
+        <v>0.2</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1907,7 +1907,7 @@
         <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2</v>
@@ -1942,7 +1942,7 @@
         <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1950,10 +1950,10 @@
       <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1968,7 +1968,7 @@
       <c r="Q18" s="13" t="n">
         <v>89.2</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1981,7 +1981,7 @@
         <v>10.1</v>
       </c>
       <c r="V18" s="13" t="n">
-        <v>12.18</v>
+        <v>1.8</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>30.6</v>
@@ -2035,17 +2035,17 @@
       <c r="K19" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>18.2</v>
+      <c r="L19" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.2</v>
@@ -2053,14 +2053,14 @@
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>0.2</v>
@@ -2075,7 +2075,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.2</v>
+        <v>87.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>28.5</v>
@@ -2105,8 +2105,8 @@
       <c r="F20" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>29.6</v>
+      <c r="G20" s="8" t="n">
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2115,15 +2115,15 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -2136,7 +2136,7 @@
       <c r="Q20" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2155,7 +2155,7 @@
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>25.3</v>
+        <v>85.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>28.4</v>
@@ -2195,7 +2195,7 @@
         <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1.9</v>
@@ -2203,14 +2203,14 @@
       <c r="K21" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
@@ -2221,14 +2221,14 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>28.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.2</v>
@@ -2240,10 +2240,10 @@
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2262,18 +2262,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>29.2</v>
+        <v>30.2</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>17</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G22" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2288,14 +2288,14 @@
       <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91.2</v>
@@ -2306,7 +2306,7 @@
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="R22" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2316,7 +2316,7 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.9</v>
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24.6</v>
@@ -2325,7 +2325,7 @@
         <v>26.2</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>22.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>80.2</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="14" t="n">
-        <v>147.6</v>
+        <v>147.5</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>90.40000000000001</v>
@@ -2378,26 +2378,26 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>451.2</v>
+        <v>45.7</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="8" t="n">
-        <v>107.2</v>
+      <c r="R23" s="14" t="n">
+        <v>107.8</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>34.7</v>
+        <v>57.7</v>
       </c>
       <c r="V23" s="14" t="n">
         <v>108.4</v>
@@ -2406,7 +2406,7 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.8</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>427.6</v>
@@ -2452,19 +2452,19 @@
         <v>1.8</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L24" s="14" t="n">
         <v>18.8</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="14" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>31.2</v>
+        <v>81.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
@@ -2472,14 +2472,14 @@
       <c r="Q24" s="14" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="8" t="n">
-        <v>21.4</v>
+      <c r="R24" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.2</v>
+        <v>78.8</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2497,7 +2497,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>18.7</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>44.4</v>
@@ -2537,17 +2537,17 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>92.2</v>
+        <v>0.9</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>28.6</v>
@@ -2606,13 +2606,13 @@
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2620,17 +2620,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2639,13 +2639,13 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>76.2</v>
+        <v>7.6</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2657,7 +2657,7 @@
         <v>21.3</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
@@ -2692,7 +2692,7 @@
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2701,25 +2701,25 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2728,7 +2728,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>0.1</v>
+        <v>6.3</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2786,20 +2786,20 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.1</v>
@@ -2817,16 +2817,16 @@
         <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>216.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>53.2</v>
@@ -2869,12 +2869,12 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="M29" s="12" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90.59999999999999</v>
@@ -2904,7 +2904,7 @@
         <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
@@ -2933,7 +2933,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>119.1</v>
+        <v>119</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>58.8</v>
@@ -2954,11 +2954,11 @@
         <v>92.5</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>92.09999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2979,13 +2979,13 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="14" t="n">
-        <v>104.6</v>
+        <v>10.4</v>
       </c>
       <c r="W30" s="14" t="n">
-        <v>114.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>372.2</v>
+        <v>382.8</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>32.4</v>
@@ -3007,20 +3007,20 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>22.9</v>
+      <c r="E31" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
@@ -3029,14 +3029,14 @@
         <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="14" t="n">
-        <v>18.9</v>
+      <c r="L31" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="M31" s="14" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="R31" s="14" t="n">
         <v>22.6</v>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>32.8</v>
@@ -3114,12 +3114,12 @@
       <c r="K32" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="12" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>91.2</v>
@@ -3130,7 +3130,7 @@
       <c r="Q32" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3142,7 +3142,7 @@
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W32" s="8" t="n">
@@ -3180,8 +3180,8 @@
       <c r="F33" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>94.59999999999999</v>
+      <c r="G33" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3195,7 +3195,7 @@
       <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="M33" s="13" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>90.3</v>
+        <v>80.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3211,20 +3211,20 @@
       <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>24.8</v>
+      <c r="R33" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.2</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>22</v>
+        <v>24.2</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="W33" s="8" t="n">
         <v>27.4</v>
@@ -3278,17 +3278,17 @@
       <c r="K34" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>19.7</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
@@ -3296,7 +3296,7 @@
       <c r="Q34" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3308,14 +3308,14 @@
       <c r="U34" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W34" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>86.3</v>
+        <v>8.6</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>6.7</v>
@@ -3337,19 +3337,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>18.4</v>
+        <v>24.4</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>12</v>
+        <v>27.4</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.2</v>
@@ -3363,25 +3363,25 @@
       <c r="K35" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="8" t="n">
         <v>19</v>
       </c>
       <c r="M35" s="13" t="n">
         <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3391,9 +3391,9 @@
         <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W35" s="8" t="n">
@@ -3441,22 +3441,22 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3464,7 +3464,7 @@
       <c r="Q36" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3476,7 +3476,7 @@
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="8" t="n">
+      <c r="V36" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="W36" s="8" t="n">
@@ -3486,7 +3486,7 @@
         <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>17.6</v>
@@ -3509,9 +3509,9 @@
         <v>161.5</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F37" s="8" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F37" s="14" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3533,13 +3533,13 @@
         <v>95.09999999999999</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.4</v>
+        <v>450</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.6</v>
@@ -3547,11 +3547,11 @@
       <c r="Q37" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="8" t="n">
+      <c r="R37" s="14" t="n">
         <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>190.4</v>
+        <v>19</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3559,7 +3559,7 @@
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="8" t="n">
+      <c r="V37" s="14" t="n">
         <v>110</v>
       </c>
       <c r="W37" s="8" t="n">
@@ -3572,7 +3572,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.2</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3588,16 +3588,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="8" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E38" s="8" t="n">
+      <c r="D38" s="14" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E38" s="14" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G38" s="8" t="n">
+      <c r="F38" s="14" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3610,39 +3610,39 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="14" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="M38" s="14" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R38" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q38" s="14" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="R38" s="14" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>49.2</v>
+        <v>4.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="8" t="n">
+      <c r="V38" s="14" t="n">
         <v>22.2</v>
       </c>
       <c r="W38" s="8" t="n">
@@ -3652,10 +3652,10 @@
         <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3698,17 +3698,17 @@
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>32.5</v>
@@ -3781,19 +3781,19 @@
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>18.2</v>
+      <c r="M40" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>29.8</v>
+        <v>2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="8" t="n">
         <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3806,7 +3806,7 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
@@ -3815,13 +3815,13 @@
         <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3846,8 +3846,8 @@
       <c r="F41" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>82.8</v>
+      <c r="G41" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3864,7 +3864,7 @@
       <c r="L41" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3874,7 +3874,7 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3884,7 +3884,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3896,7 +3896,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3929,7 +3929,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3943,11 +3943,11 @@
       <c r="L42" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3955,7 +3955,7 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="8" t="n">
         <v>25</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -3965,13 +3965,13 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="V42" s="13" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="W42" s="13" t="n">
         <v>0.2</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
       <c r="E43" s="12" t="inlineStr"/>
@@ -4004,11 +4004,11 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="12" t="inlineStr"/>
       <c r="E44" s="12" t="inlineStr"/>
@@ -4043,11 +4043,11 @@
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="8" t="inlineStr"/>
       <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
       <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4071,16 +4071,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="14" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="F45" s="14" t="n">
+      <c r="D45" s="8" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="F45" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="8" t="n">
         <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4096,32 +4096,32 @@
         <v>7.7</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>14.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>11.1</v>
+        <v>31.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>266.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="14" t="n">
-        <v>106.9</v>
+      <c r="Q45" s="8" t="n">
+        <v>106.7</v>
       </c>
       <c r="R45" s="14" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>24.1</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.3</v>
+        <v>95.3</v>
       </c>
       <c r="V45" s="14" t="n">
         <v>85.7</v>
@@ -4130,13 +4130,13 @@
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>327.2</v>
+        <v>32.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>13.7</v>
@@ -4179,17 +4179,17 @@
       <c r="L46" s="14" t="n">
         <v>12.4</v>
       </c>
-      <c r="M46" s="14" t="n">
-        <v>19.9</v>
+      <c r="M46" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="Q46" s="14" t="n">
         <v>0.2</v>
@@ -4201,7 +4201,7 @@
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>29.8</v>
@@ -4215,9 +4215,7 @@
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
         <v>298.9</v>
       </c>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -159,6 +165,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1179,7 +1188,7 @@
       <c r="J9" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>44.2</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1726,7 +1735,7 @@
       <c r="J16" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="11" t="n"/>
       <c r="L16" s="3" t="n">
         <v>951.3</v>
       </c>
@@ -2275,7 +2284,7 @@
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>96.2</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2435,7 +2444,7 @@
       <c r="J25" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="9" t="n">
         <v>8</v>
       </c>
       <c r="L25" s="3" t="n">
@@ -2514,7 +2523,7 @@
       <c r="J26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="9" t="n">
         <v>2.5</v>
       </c>
       <c r="L26" s="3" t="n">
@@ -2595,7 +2604,7 @@
       <c r="J27" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
@@ -2674,7 +2683,7 @@
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
@@ -2755,7 +2764,7 @@
       <c r="J29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L29" s="3" t="n">
@@ -2836,7 +2845,7 @@
       <c r="J30" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>11.3</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3387,7 +3396,7 @@
       <c r="J37" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>49.9</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4007,7 +4016,7 @@
       <c r="J45" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>8.5</v>
       </c>
       <c r="L45" s="3" t="n">
